--- a/src/fnschool/canteen/data/consuming.xlsx
+++ b/src/fnschool/canteen/data/consuming.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">食材名称</t>
   </si>
@@ -414,31 +411,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CF214"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:CE214"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="1" width="25.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="13.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="12.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="15.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="14.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="13.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="12.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="15.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="14.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="5"/>
+      <c r="A1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
@@ -447,341 +443,338 @@
       <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>4</v>
+      <c r="E2" s="9" t="str">
+        <f aca="false">IF(ISBLANK(E$1),"",SUMPRODUCT($D$3:$D$1024,E$3:E$1024))</f>
+        <v/>
       </c>
       <c r="F2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(F$1),"",SUMPRODUCT($E$3:$E$1024,F$3:F$1024))</f>
+        <f aca="false">IF(ISBLANK(F$1),"",SUMPRODUCT($D$3:$D$1024,F$3:F$1024))</f>
         <v/>
       </c>
       <c r="G2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(G$1),"",SUMPRODUCT($E$3:$E$1024,G$3:G$1024))</f>
+        <f aca="false">IF(ISBLANK(G$1),"",SUMPRODUCT($D$3:$D$1024,G$3:G$1024))</f>
         <v/>
       </c>
       <c r="H2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(H$1),"",SUMPRODUCT($E$3:$E$1024,H$3:H$1024))</f>
+        <f aca="false">IF(ISBLANK(H$1),"",SUMPRODUCT($D$3:$D$1024,H$3:H$1024))</f>
         <v/>
       </c>
       <c r="I2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(I$1),"",SUMPRODUCT($E$3:$E$1024,I$3:I$1024))</f>
+        <f aca="false">IF(ISBLANK(I$1),"",SUMPRODUCT($D$3:$D$1024,I$3:I$1024))</f>
         <v/>
       </c>
       <c r="J2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(J$1),"",SUMPRODUCT($E$3:$E$1024,J$3:J$1024))</f>
+        <f aca="false">IF(ISBLANK(J$1),"",SUMPRODUCT($D$3:$D$1024,J$3:J$1024))</f>
         <v/>
       </c>
       <c r="K2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(K$1),"",SUMPRODUCT($E$3:$E$1024,K$3:K$1024))</f>
+        <f aca="false">IF(ISBLANK(K$1),"",SUMPRODUCT($D$3:$D$1024,K$3:K$1024))</f>
         <v/>
       </c>
       <c r="L2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(L$1),"",SUMPRODUCT($E$3:$E$1024,L$3:L$1024))</f>
+        <f aca="false">IF(ISBLANK(L$1),"",SUMPRODUCT($D$3:$D$1024,L$3:L$1024))</f>
         <v/>
       </c>
       <c r="M2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(M$1),"",SUMPRODUCT($E$3:$E$1024,M$3:M$1024))</f>
+        <f aca="false">IF(ISBLANK(M$1),"",SUMPRODUCT($D$3:$D$1024,M$3:M$1024))</f>
         <v/>
       </c>
       <c r="N2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(N$1),"",SUMPRODUCT($E$3:$E$1024,N$3:N$1024))</f>
+        <f aca="false">IF(ISBLANK(N$1),"",SUMPRODUCT($D$3:$D$1024,N$3:N$1024))</f>
         <v/>
       </c>
       <c r="O2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(O$1),"",SUMPRODUCT($E$3:$E$1024,O$3:O$1024))</f>
+        <f aca="false">IF(ISBLANK(O$1),"",SUMPRODUCT($D$3:$D$1024,O$3:O$1024))</f>
         <v/>
       </c>
       <c r="P2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(P$1),"",SUMPRODUCT($E$3:$E$1024,P$3:P$1024))</f>
+        <f aca="false">IF(ISBLANK(P$1),"",SUMPRODUCT($D$3:$D$1024,P$3:P$1024))</f>
         <v/>
       </c>
       <c r="Q2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(Q$1),"",SUMPRODUCT($E$3:$E$1024,Q$3:Q$1024))</f>
+        <f aca="false">IF(ISBLANK(Q$1),"",SUMPRODUCT($D$3:$D$1024,Q$3:Q$1024))</f>
         <v/>
       </c>
       <c r="R2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(R$1),"",SUMPRODUCT($E$3:$E$1024,R$3:R$1024))</f>
+        <f aca="false">IF(ISBLANK(R$1),"",SUMPRODUCT($D$3:$D$1024,R$3:R$1024))</f>
         <v/>
       </c>
       <c r="S2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(S$1),"",SUMPRODUCT($E$3:$E$1024,S$3:S$1024))</f>
+        <f aca="false">IF(ISBLANK(S$1),"",SUMPRODUCT($D$3:$D$1024,S$3:S$1024))</f>
         <v/>
       </c>
       <c r="T2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(T$1),"",SUMPRODUCT($E$3:$E$1024,T$3:T$1024))</f>
+        <f aca="false">IF(ISBLANK(T$1),"",SUMPRODUCT($D$3:$D$1024,T$3:T$1024))</f>
         <v/>
       </c>
       <c r="U2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(U$1),"",SUMPRODUCT($E$3:$E$1024,U$3:U$1024))</f>
+        <f aca="false">IF(ISBLANK(U$1),"",SUMPRODUCT($D$3:$D$1024,U$3:U$1024))</f>
         <v/>
       </c>
       <c r="V2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(V$1),"",SUMPRODUCT($E$3:$E$1024,V$3:V$1024))</f>
+        <f aca="false">IF(ISBLANK(V$1),"",SUMPRODUCT($D$3:$D$1024,V$3:V$1024))</f>
         <v/>
       </c>
       <c r="W2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(W$1),"",SUMPRODUCT($E$3:$E$1024,W$3:W$1024))</f>
+        <f aca="false">IF(ISBLANK(W$1),"",SUMPRODUCT($D$3:$D$1024,W$3:W$1024))</f>
         <v/>
       </c>
       <c r="X2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(X$1),"",SUMPRODUCT($E$3:$E$1024,X$3:X$1024))</f>
+        <f aca="false">IF(ISBLANK(X$1),"",SUMPRODUCT($D$3:$D$1024,X$3:X$1024))</f>
         <v/>
       </c>
       <c r="Y2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(Y$1),"",SUMPRODUCT($E$3:$E$1024,Y$3:Y$1024))</f>
+        <f aca="false">IF(ISBLANK(Y$1),"",SUMPRODUCT($D$3:$D$1024,Y$3:Y$1024))</f>
         <v/>
       </c>
       <c r="Z2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(Z$1),"",SUMPRODUCT($E$3:$E$1024,Z$3:Z$1024))</f>
+        <f aca="false">IF(ISBLANK(Z$1),"",SUMPRODUCT($D$3:$D$1024,Z$3:Z$1024))</f>
         <v/>
       </c>
       <c r="AA2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AA$1),"",SUMPRODUCT($E$3:$E$1024,AA$3:AA$1024))</f>
+        <f aca="false">IF(ISBLANK(AA$1),"",SUMPRODUCT($D$3:$D$1024,AA$3:AA$1024))</f>
         <v/>
       </c>
       <c r="AB2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AB$1),"",SUMPRODUCT($E$3:$E$1024,AB$3:AB$1024))</f>
+        <f aca="false">IF(ISBLANK(AB$1),"",SUMPRODUCT($D$3:$D$1024,AB$3:AB$1024))</f>
         <v/>
       </c>
       <c r="AC2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AC$1),"",SUMPRODUCT($E$3:$E$1024,AC$3:AC$1024))</f>
+        <f aca="false">IF(ISBLANK(AC$1),"",SUMPRODUCT($D$3:$D$1024,AC$3:AC$1024))</f>
         <v/>
       </c>
       <c r="AD2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AD$1),"",SUMPRODUCT($E$3:$E$1024,AD$3:AD$1024))</f>
+        <f aca="false">IF(ISBLANK(AD$1),"",SUMPRODUCT($D$3:$D$1024,AD$3:AD$1024))</f>
         <v/>
       </c>
       <c r="AE2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AE$1),"",SUMPRODUCT($E$3:$E$1024,AE$3:AE$1024))</f>
+        <f aca="false">IF(ISBLANK(AE$1),"",SUMPRODUCT($D$3:$D$1024,AE$3:AE$1024))</f>
         <v/>
       </c>
       <c r="AF2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AF$1),"",SUMPRODUCT($E$3:$E$1024,AF$3:AF$1024))</f>
+        <f aca="false">IF(ISBLANK(AF$1),"",SUMPRODUCT($D$3:$D$1024,AF$3:AF$1024))</f>
         <v/>
       </c>
       <c r="AG2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AG$1),"",SUMPRODUCT($E$3:$E$1024,AG$3:AG$1024))</f>
+        <f aca="false">IF(ISBLANK(AG$1),"",SUMPRODUCT($D$3:$D$1024,AG$3:AG$1024))</f>
         <v/>
       </c>
       <c r="AH2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AH$1),"",SUMPRODUCT($E$3:$E$1024,AH$3:AH$1024))</f>
+        <f aca="false">IF(ISBLANK(AH$1),"",SUMPRODUCT($D$3:$D$1024,AH$3:AH$1024))</f>
         <v/>
       </c>
       <c r="AI2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AI$1),"",SUMPRODUCT($E$3:$E$1024,AI$3:AI$1024))</f>
+        <f aca="false">IF(ISBLANK(AI$1),"",SUMPRODUCT($D$3:$D$1024,AI$3:AI$1024))</f>
         <v/>
       </c>
       <c r="AJ2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AJ$1),"",SUMPRODUCT($E$3:$E$1024,AJ$3:AJ$1024))</f>
+        <f aca="false">IF(ISBLANK(AJ$1),"",SUMPRODUCT($D$3:$D$1024,AJ$3:AJ$1024))</f>
         <v/>
       </c>
       <c r="AK2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AK$1),"",SUMPRODUCT($E$3:$E$1024,AK$3:AK$1024))</f>
+        <f aca="false">IF(ISBLANK(AK$1),"",SUMPRODUCT($D$3:$D$1024,AK$3:AK$1024))</f>
         <v/>
       </c>
       <c r="AL2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AL$1),"",SUMPRODUCT($E$3:$E$1024,AL$3:AL$1024))</f>
+        <f aca="false">IF(ISBLANK(AL$1),"",SUMPRODUCT($D$3:$D$1024,AL$3:AL$1024))</f>
         <v/>
       </c>
       <c r="AM2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AM$1),"",SUMPRODUCT($E$3:$E$1024,AM$3:AM$1024))</f>
+        <f aca="false">IF(ISBLANK(AM$1),"",SUMPRODUCT($D$3:$D$1024,AM$3:AM$1024))</f>
         <v/>
       </c>
       <c r="AN2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AN$1),"",SUMPRODUCT($E$3:$E$1024,AN$3:AN$1024))</f>
+        <f aca="false">IF(ISBLANK(AN$1),"",SUMPRODUCT($D$3:$D$1024,AN$3:AN$1024))</f>
         <v/>
       </c>
       <c r="AO2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AO$1),"",SUMPRODUCT($E$3:$E$1024,AO$3:AO$1024))</f>
+        <f aca="false">IF(ISBLANK(AO$1),"",SUMPRODUCT($D$3:$D$1024,AO$3:AO$1024))</f>
         <v/>
       </c>
       <c r="AP2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AP$1),"",SUMPRODUCT($E$3:$E$1024,AP$3:AP$1024))</f>
+        <f aca="false">IF(ISBLANK(AP$1),"",SUMPRODUCT($D$3:$D$1024,AP$3:AP$1024))</f>
         <v/>
       </c>
       <c r="AQ2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AQ$1),"",SUMPRODUCT($E$3:$E$1024,AQ$3:AQ$1024))</f>
+        <f aca="false">IF(ISBLANK(AQ$1),"",SUMPRODUCT($D$3:$D$1024,AQ$3:AQ$1024))</f>
         <v/>
       </c>
       <c r="AR2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AR$1),"",SUMPRODUCT($E$3:$E$1024,AR$3:AR$1024))</f>
+        <f aca="false">IF(ISBLANK(AR$1),"",SUMPRODUCT($D$3:$D$1024,AR$3:AR$1024))</f>
         <v/>
       </c>
       <c r="AS2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AS$1),"",SUMPRODUCT($E$3:$E$1024,AS$3:AS$1024))</f>
+        <f aca="false">IF(ISBLANK(AS$1),"",SUMPRODUCT($D$3:$D$1024,AS$3:AS$1024))</f>
         <v/>
       </c>
       <c r="AT2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AT$1),"",SUMPRODUCT($E$3:$E$1024,AT$3:AT$1024))</f>
+        <f aca="false">IF(ISBLANK(AT$1),"",SUMPRODUCT($D$3:$D$1024,AT$3:AT$1024))</f>
         <v/>
       </c>
       <c r="AU2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AU$1),"",SUMPRODUCT($E$3:$E$1024,AU$3:AU$1024))</f>
+        <f aca="false">IF(ISBLANK(AU$1),"",SUMPRODUCT($D$3:$D$1024,AU$3:AU$1024))</f>
         <v/>
       </c>
       <c r="AV2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AV$1),"",SUMPRODUCT($E$3:$E$1024,AV$3:AV$1024))</f>
+        <f aca="false">IF(ISBLANK(AV$1),"",SUMPRODUCT($D$3:$D$1024,AV$3:AV$1024))</f>
         <v/>
       </c>
       <c r="AW2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AW$1),"",SUMPRODUCT($E$3:$E$1024,AW$3:AW$1024))</f>
+        <f aca="false">IF(ISBLANK(AW$1),"",SUMPRODUCT($D$3:$D$1024,AW$3:AW$1024))</f>
         <v/>
       </c>
       <c r="AX2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AX$1),"",SUMPRODUCT($E$3:$E$1024,AX$3:AX$1024))</f>
+        <f aca="false">IF(ISBLANK(AX$1),"",SUMPRODUCT($D$3:$D$1024,AX$3:AX$1024))</f>
         <v/>
       </c>
       <c r="AY2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AY$1),"",SUMPRODUCT($E$3:$E$1024,AY$3:AY$1024))</f>
+        <f aca="false">IF(ISBLANK(AY$1),"",SUMPRODUCT($D$3:$D$1024,AY$3:AY$1024))</f>
         <v/>
       </c>
       <c r="AZ2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(AZ$1),"",SUMPRODUCT($E$3:$E$1024,AZ$3:AZ$1024))</f>
+        <f aca="false">IF(ISBLANK(AZ$1),"",SUMPRODUCT($D$3:$D$1024,AZ$3:AZ$1024))</f>
         <v/>
       </c>
       <c r="BA2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BA$1),"",SUMPRODUCT($E$3:$E$1024,BA$3:BA$1024))</f>
+        <f aca="false">IF(ISBLANK(BA$1),"",SUMPRODUCT($D$3:$D$1024,BA$3:BA$1024))</f>
         <v/>
       </c>
       <c r="BB2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BB$1),"",SUMPRODUCT($E$3:$E$1024,BB$3:BB$1024))</f>
+        <f aca="false">IF(ISBLANK(BB$1),"",SUMPRODUCT($D$3:$D$1024,BB$3:BB$1024))</f>
         <v/>
       </c>
       <c r="BC2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BC$1),"",SUMPRODUCT($E$3:$E$1024,BC$3:BC$1024))</f>
+        <f aca="false">IF(ISBLANK(BC$1),"",SUMPRODUCT($D$3:$D$1024,BC$3:BC$1024))</f>
         <v/>
       </c>
       <c r="BD2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BD$1),"",SUMPRODUCT($E$3:$E$1024,BD$3:BD$1024))</f>
+        <f aca="false">IF(ISBLANK(BD$1),"",SUMPRODUCT($D$3:$D$1024,BD$3:BD$1024))</f>
         <v/>
       </c>
       <c r="BE2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BE$1),"",SUMPRODUCT($E$3:$E$1024,BE$3:BE$1024))</f>
+        <f aca="false">IF(ISBLANK(BE$1),"",SUMPRODUCT($D$3:$D$1024,BE$3:BE$1024))</f>
         <v/>
       </c>
       <c r="BF2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BF$1),"",SUMPRODUCT($E$3:$E$1024,BF$3:BF$1024))</f>
+        <f aca="false">IF(ISBLANK(BF$1),"",SUMPRODUCT($D$3:$D$1024,BF$3:BF$1024))</f>
         <v/>
       </c>
       <c r="BG2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BG$1),"",SUMPRODUCT($E$3:$E$1024,BG$3:BG$1024))</f>
+        <f aca="false">IF(ISBLANK(BG$1),"",SUMPRODUCT($D$3:$D$1024,BG$3:BG$1024))</f>
         <v/>
       </c>
       <c r="BH2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BH$1),"",SUMPRODUCT($E$3:$E$1024,BH$3:BH$1024))</f>
+        <f aca="false">IF(ISBLANK(BH$1),"",SUMPRODUCT($D$3:$D$1024,BH$3:BH$1024))</f>
         <v/>
       </c>
       <c r="BI2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BI$1),"",SUMPRODUCT($E$3:$E$1024,BI$3:BI$1024))</f>
+        <f aca="false">IF(ISBLANK(BI$1),"",SUMPRODUCT($D$3:$D$1024,BI$3:BI$1024))</f>
         <v/>
       </c>
       <c r="BJ2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BJ$1),"",SUMPRODUCT($E$3:$E$1024,BJ$3:BJ$1024))</f>
+        <f aca="false">IF(ISBLANK(BJ$1),"",SUMPRODUCT($D$3:$D$1024,BJ$3:BJ$1024))</f>
         <v/>
       </c>
       <c r="BK2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BK$1),"",SUMPRODUCT($E$3:$E$1024,BK$3:BK$1024))</f>
+        <f aca="false">IF(ISBLANK(BK$1),"",SUMPRODUCT($D$3:$D$1024,BK$3:BK$1024))</f>
         <v/>
       </c>
       <c r="BL2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BL$1),"",SUMPRODUCT($E$3:$E$1024,BL$3:BL$1024))</f>
+        <f aca="false">IF(ISBLANK(BL$1),"",SUMPRODUCT($D$3:$D$1024,BL$3:BL$1024))</f>
         <v/>
       </c>
       <c r="BM2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BM$1),"",SUMPRODUCT($E$3:$E$1024,BM$3:BM$1024))</f>
+        <f aca="false">IF(ISBLANK(BM$1),"",SUMPRODUCT($D$3:$D$1024,BM$3:BM$1024))</f>
         <v/>
       </c>
       <c r="BN2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BN$1),"",SUMPRODUCT($E$3:$E$1024,BN$3:BN$1024))</f>
+        <f aca="false">IF(ISBLANK(BN$1),"",SUMPRODUCT($D$3:$D$1024,BN$3:BN$1024))</f>
         <v/>
       </c>
       <c r="BO2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BO$1),"",SUMPRODUCT($E$3:$E$1024,BO$3:BO$1024))</f>
+        <f aca="false">IF(ISBLANK(BO$1),"",SUMPRODUCT($D$3:$D$1024,BO$3:BO$1024))</f>
         <v/>
       </c>
       <c r="BP2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BP$1),"",SUMPRODUCT($E$3:$E$1024,BP$3:BP$1024))</f>
+        <f aca="false">IF(ISBLANK(BP$1),"",SUMPRODUCT($D$3:$D$1024,BP$3:BP$1024))</f>
         <v/>
       </c>
       <c r="BQ2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BQ$1),"",SUMPRODUCT($E$3:$E$1024,BQ$3:BQ$1024))</f>
+        <f aca="false">IF(ISBLANK(BQ$1),"",SUMPRODUCT($D$3:$D$1024,BQ$3:BQ$1024))</f>
         <v/>
       </c>
       <c r="BR2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BR$1),"",SUMPRODUCT($E$3:$E$1024,BR$3:BR$1024))</f>
+        <f aca="false">IF(ISBLANK(BR$1),"",SUMPRODUCT($D$3:$D$1024,BR$3:BR$1024))</f>
         <v/>
       </c>
       <c r="BS2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BS$1),"",SUMPRODUCT($E$3:$E$1024,BS$3:BS$1024))</f>
+        <f aca="false">IF(ISBLANK(BS$1),"",SUMPRODUCT($D$3:$D$1024,BS$3:BS$1024))</f>
         <v/>
       </c>
       <c r="BT2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BT$1),"",SUMPRODUCT($E$3:$E$1024,BT$3:BT$1024))</f>
+        <f aca="false">IF(ISBLANK(BT$1),"",SUMPRODUCT($D$3:$D$1024,BT$3:BT$1024))</f>
         <v/>
       </c>
       <c r="BU2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BU$1),"",SUMPRODUCT($E$3:$E$1024,BU$3:BU$1024))</f>
+        <f aca="false">IF(ISBLANK(BU$1),"",SUMPRODUCT($D$3:$D$1024,BU$3:BU$1024))</f>
         <v/>
       </c>
       <c r="BV2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BV$1),"",SUMPRODUCT($E$3:$E$1024,BV$3:BV$1024))</f>
+        <f aca="false">IF(ISBLANK(BV$1),"",SUMPRODUCT($D$3:$D$1024,BV$3:BV$1024))</f>
         <v/>
       </c>
       <c r="BW2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BW$1),"",SUMPRODUCT($E$3:$E$1024,BW$3:BW$1024))</f>
+        <f aca="false">IF(ISBLANK(BW$1),"",SUMPRODUCT($D$3:$D$1024,BW$3:BW$1024))</f>
         <v/>
       </c>
       <c r="BX2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BX$1),"",SUMPRODUCT($E$3:$E$1024,BX$3:BX$1024))</f>
+        <f aca="false">IF(ISBLANK(BX$1),"",SUMPRODUCT($D$3:$D$1024,BX$3:BX$1024))</f>
         <v/>
       </c>
       <c r="BY2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BY$1),"",SUMPRODUCT($E$3:$E$1024,BY$3:BY$1024))</f>
+        <f aca="false">IF(ISBLANK(BY$1),"",SUMPRODUCT($D$3:$D$1024,BY$3:BY$1024))</f>
         <v/>
       </c>
       <c r="BZ2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(BZ$1),"",SUMPRODUCT($E$3:$E$1024,BZ$3:BZ$1024))</f>
+        <f aca="false">IF(ISBLANK(BZ$1),"",SUMPRODUCT($D$3:$D$1024,BZ$3:BZ$1024))</f>
         <v/>
       </c>
       <c r="CA2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(CA$1),"",SUMPRODUCT($E$3:$E$1024,CA$3:CA$1024))</f>
+        <f aca="false">IF(ISBLANK(CA$1),"",SUMPRODUCT($D$3:$D$1024,CA$3:CA$1024))</f>
         <v/>
       </c>
       <c r="CB2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(CB$1),"",SUMPRODUCT($E$3:$E$1024,CB$3:CB$1024))</f>
+        <f aca="false">IF(ISBLANK(CB$1),"",SUMPRODUCT($D$3:$D$1024,CB$3:CB$1024))</f>
         <v/>
       </c>
       <c r="CC2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(CC$1),"",SUMPRODUCT($E$3:$E$1024,CC$3:CC$1024))</f>
+        <f aca="false">IF(ISBLANK(CC$1),"",SUMPRODUCT($D$3:$D$1024,CC$3:CC$1024))</f>
         <v/>
       </c>
       <c r="CD2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(CD$1),"",SUMPRODUCT($E$3:$E$1024,CD$3:CD$1024))</f>
+        <f aca="false">IF(ISBLANK(CD$1),"",SUMPRODUCT($D$3:$D$1024,CD$3:CD$1024))</f>
         <v/>
       </c>
       <c r="CE2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(CE$1),"",SUMPRODUCT($E$3:$E$1024,CE$3:CE$1024))</f>
-        <v/>
-      </c>
-      <c r="CF2" s="9" t="str">
-        <f aca="false">IF(ISBLANK(CF$1),"",SUMPRODUCT($E$3:$E$1024,CF$3:CF$1024))</f>
+        <f aca="false">IF(ISBLANK(CE$1),"",SUMPRODUCT($D$3:$D$1024,CE$3:CE$1024))</f>
         <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E3" s="12"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
@@ -860,17 +853,16 @@
       <c r="CC3" s="10"/>
       <c r="CD3" s="10"/>
       <c r="CE3" s="10"/>
-      <c r="CF3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E4" s="12"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -949,17 +941,16 @@
       <c r="CC4" s="10"/>
       <c r="CD4" s="10"/>
       <c r="CE4" s="10"/>
-      <c r="CF4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E5" s="13"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -1038,17 +1029,16 @@
       <c r="CC5" s="10"/>
       <c r="CD5" s="10"/>
       <c r="CE5" s="10"/>
-      <c r="CF5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E6" s="12"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
@@ -1127,17 +1117,16 @@
       <c r="CC6" s="10"/>
       <c r="CD6" s="10"/>
       <c r="CE6" s="10"/>
-      <c r="CF6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E7" s="12"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -1216,17 +1205,16 @@
       <c r="CC7" s="10"/>
       <c r="CD7" s="10"/>
       <c r="CE7" s="10"/>
-      <c r="CF7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E8" s="12"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -1305,17 +1293,16 @@
       <c r="CC8" s="10"/>
       <c r="CD8" s="10"/>
       <c r="CE8" s="10"/>
-      <c r="CF8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E9" s="12"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -1394,17 +1381,16 @@
       <c r="CC9" s="10"/>
       <c r="CD9" s="10"/>
       <c r="CE9" s="10"/>
-      <c r="CF9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E10" s="12"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -1483,17 +1469,16 @@
       <c r="CC10" s="10"/>
       <c r="CD10" s="10"/>
       <c r="CE10" s="10"/>
-      <c r="CF10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E11" s="12"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -1572,17 +1557,16 @@
       <c r="CC11" s="10"/>
       <c r="CD11" s="10"/>
       <c r="CE11" s="10"/>
-      <c r="CF11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E12" s="12"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
@@ -1661,17 +1645,16 @@
       <c r="CC12" s="10"/>
       <c r="CD12" s="10"/>
       <c r="CE12" s="10"/>
-      <c r="CF12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E13" s="12"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
@@ -1750,17 +1733,16 @@
       <c r="CC13" s="10"/>
       <c r="CD13" s="10"/>
       <c r="CE13" s="10"/>
-      <c r="CF13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E14" s="12"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -1839,17 +1821,16 @@
       <c r="CC14" s="10"/>
       <c r="CD14" s="10"/>
       <c r="CE14" s="10"/>
-      <c r="CF14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E15" s="12"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -1928,17 +1909,16 @@
       <c r="CC15" s="10"/>
       <c r="CD15" s="10"/>
       <c r="CE15" s="10"/>
-      <c r="CF15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E16" s="13"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
@@ -2017,17 +1997,16 @@
       <c r="CC16" s="10"/>
       <c r="CD16" s="10"/>
       <c r="CE16" s="10"/>
-      <c r="CF16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E17" s="13"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
@@ -2106,17 +2085,16 @@
       <c r="CC17" s="10"/>
       <c r="CD17" s="10"/>
       <c r="CE17" s="10"/>
-      <c r="CF17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E18" s="12"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
@@ -2195,17 +2173,16 @@
       <c r="CC18" s="10"/>
       <c r="CD18" s="10"/>
       <c r="CE18" s="10"/>
-      <c r="CF18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E19" s="13"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -2284,17 +2261,16 @@
       <c r="CC19" s="10"/>
       <c r="CD19" s="10"/>
       <c r="CE19" s="10"/>
-      <c r="CF19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E20" s="12"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
@@ -2373,17 +2349,16 @@
       <c r="CC20" s="10"/>
       <c r="CD20" s="10"/>
       <c r="CE20" s="10"/>
-      <c r="CF20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E21" s="12"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
@@ -2462,17 +2437,16 @@
       <c r="CC21" s="10"/>
       <c r="CD21" s="10"/>
       <c r="CE21" s="10"/>
-      <c r="CF21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E22" s="12"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -2551,17 +2525,16 @@
       <c r="CC22" s="10"/>
       <c r="CD22" s="10"/>
       <c r="CE22" s="10"/>
-      <c r="CF22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E23" s="13"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
@@ -2640,17 +2613,16 @@
       <c r="CC23" s="10"/>
       <c r="CD23" s="10"/>
       <c r="CE23" s="10"/>
-      <c r="CF23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E24" s="12"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -2729,17 +2701,16 @@
       <c r="CC24" s="10"/>
       <c r="CD24" s="10"/>
       <c r="CE24" s="10"/>
-      <c r="CF24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E25" s="12"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -2818,17 +2789,16 @@
       <c r="CC25" s="10"/>
       <c r="CD25" s="10"/>
       <c r="CE25" s="10"/>
-      <c r="CF25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E26" s="12"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
@@ -2907,17 +2877,16 @@
       <c r="CC26" s="10"/>
       <c r="CD26" s="10"/>
       <c r="CE26" s="10"/>
-      <c r="CF26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E27" s="12"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
@@ -2996,17 +2965,16 @@
       <c r="CC27" s="10"/>
       <c r="CD27" s="10"/>
       <c r="CE27" s="10"/>
-      <c r="CF27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E28" s="12"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
@@ -3085,17 +3053,16 @@
       <c r="CC28" s="10"/>
       <c r="CD28" s="10"/>
       <c r="CE28" s="10"/>
-      <c r="CF28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E29" s="12"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
@@ -3174,17 +3141,16 @@
       <c r="CC29" s="10"/>
       <c r="CD29" s="10"/>
       <c r="CE29" s="10"/>
-      <c r="CF29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E30" s="12"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
@@ -3263,17 +3229,16 @@
       <c r="CC30" s="10"/>
       <c r="CD30" s="10"/>
       <c r="CE30" s="10"/>
-      <c r="CF30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E31" s="12"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
@@ -3352,17 +3317,16 @@
       <c r="CC31" s="10"/>
       <c r="CD31" s="10"/>
       <c r="CE31" s="10"/>
-      <c r="CF31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E32" s="12"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
@@ -3441,17 +3405,16 @@
       <c r="CC32" s="10"/>
       <c r="CD32" s="10"/>
       <c r="CE32" s="10"/>
-      <c r="CF32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E33" s="12"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
@@ -3530,17 +3493,16 @@
       <c r="CC33" s="10"/>
       <c r="CD33" s="10"/>
       <c r="CE33" s="10"/>
-      <c r="CF33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E34" s="12"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D34" s="12"/>
+      <c r="E34" s="10"/>
       <c r="F34" s="10"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
@@ -3619,17 +3581,16 @@
       <c r="CC34" s="10"/>
       <c r="CD34" s="10"/>
       <c r="CE34" s="10"/>
-      <c r="CF34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E35" s="12"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
@@ -3708,17 +3669,16 @@
       <c r="CC35" s="10"/>
       <c r="CD35" s="10"/>
       <c r="CE35" s="10"/>
-      <c r="CF35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E36" s="12"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D36" s="12"/>
+      <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
       <c r="H36" s="10"/>
@@ -3797,17 +3757,16 @@
       <c r="CC36" s="10"/>
       <c r="CD36" s="10"/>
       <c r="CE36" s="10"/>
-      <c r="CF36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E37" s="12"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D37" s="12"/>
+      <c r="E37" s="10"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
@@ -3886,17 +3845,16 @@
       <c r="CC37" s="10"/>
       <c r="CD37" s="10"/>
       <c r="CE37" s="10"/>
-      <c r="CF37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E38" s="12"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="10"/>
       <c r="F38" s="10"/>
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
@@ -3975,17 +3933,16 @@
       <c r="CC38" s="10"/>
       <c r="CD38" s="10"/>
       <c r="CE38" s="10"/>
-      <c r="CF38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E39" s="12"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="10"/>
       <c r="F39" s="10"/>
       <c r="G39" s="10"/>
       <c r="H39" s="10"/>
@@ -4064,17 +4021,16 @@
       <c r="CC39" s="10"/>
       <c r="CD39" s="10"/>
       <c r="CE39" s="10"/>
-      <c r="CF39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E40" s="12"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D40" s="12"/>
+      <c r="E40" s="10"/>
       <c r="F40" s="10"/>
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
@@ -4153,17 +4109,16 @@
       <c r="CC40" s="10"/>
       <c r="CD40" s="10"/>
       <c r="CE40" s="10"/>
-      <c r="CF40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E41" s="12"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D41" s="12"/>
+      <c r="E41" s="10"/>
       <c r="F41" s="10"/>
       <c r="G41" s="10"/>
       <c r="H41" s="10"/>
@@ -4242,17 +4197,16 @@
       <c r="CC41" s="10"/>
       <c r="CD41" s="10"/>
       <c r="CE41" s="10"/>
-      <c r="CF41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E42" s="12"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D42" s="12"/>
+      <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
@@ -4331,17 +4285,16 @@
       <c r="CC42" s="10"/>
       <c r="CD42" s="10"/>
       <c r="CE42" s="10"/>
-      <c r="CF42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E43" s="12"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D43" s="12"/>
+      <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
@@ -4420,17 +4373,16 @@
       <c r="CC43" s="10"/>
       <c r="CD43" s="10"/>
       <c r="CE43" s="10"/>
-      <c r="CF43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E44" s="12"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D44" s="12"/>
+      <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
@@ -4509,17 +4461,16 @@
       <c r="CC44" s="10"/>
       <c r="CD44" s="10"/>
       <c r="CE44" s="10"/>
-      <c r="CF44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E45" s="12"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45" s="10"/>
       <c r="F45" s="10"/>
       <c r="G45" s="10"/>
       <c r="H45" s="10"/>
@@ -4598,17 +4549,16 @@
       <c r="CC45" s="10"/>
       <c r="CD45" s="10"/>
       <c r="CE45" s="10"/>
-      <c r="CF45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E46" s="12"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D46" s="12"/>
+      <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="10"/>
       <c r="H46" s="10"/>
@@ -4687,17 +4637,16 @@
       <c r="CC46" s="10"/>
       <c r="CD46" s="10"/>
       <c r="CE46" s="10"/>
-      <c r="CF46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E47" s="12"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D47" s="12"/>
+      <c r="E47" s="10"/>
       <c r="F47" s="10"/>
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
@@ -4776,17 +4725,16 @@
       <c r="CC47" s="10"/>
       <c r="CD47" s="10"/>
       <c r="CE47" s="10"/>
-      <c r="CF47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E48" s="12"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D48" s="12"/>
+      <c r="E48" s="10"/>
       <c r="F48" s="10"/>
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
@@ -4865,17 +4813,16 @@
       <c r="CC48" s="10"/>
       <c r="CD48" s="10"/>
       <c r="CE48" s="10"/>
-      <c r="CF48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E49" s="12"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D49" s="12"/>
+      <c r="E49" s="10"/>
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
@@ -4954,17 +4901,16 @@
       <c r="CC49" s="10"/>
       <c r="CD49" s="10"/>
       <c r="CE49" s="10"/>
-      <c r="CF49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E50" s="12"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D50" s="12"/>
+      <c r="E50" s="10"/>
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
       <c r="H50" s="10"/>
@@ -5043,17 +4989,16 @@
       <c r="CC50" s="10"/>
       <c r="CD50" s="10"/>
       <c r="CE50" s="10"/>
-      <c r="CF50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E51" s="12"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D51" s="12"/>
+      <c r="E51" s="10"/>
       <c r="F51" s="10"/>
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
@@ -5132,17 +5077,16 @@
       <c r="CC51" s="10"/>
       <c r="CD51" s="10"/>
       <c r="CE51" s="10"/>
-      <c r="CF51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E52" s="12"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D52" s="12"/>
+      <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
@@ -5221,17 +5165,16 @@
       <c r="CC52" s="10"/>
       <c r="CD52" s="10"/>
       <c r="CE52" s="10"/>
-      <c r="CF52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E53" s="12"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D53" s="12"/>
+      <c r="E53" s="10"/>
       <c r="F53" s="10"/>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
@@ -5310,17 +5253,16 @@
       <c r="CC53" s="10"/>
       <c r="CD53" s="10"/>
       <c r="CE53" s="10"/>
-      <c r="CF53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E54" s="12"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D54" s="12"/>
+      <c r="E54" s="10"/>
       <c r="F54" s="10"/>
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
@@ -5399,17 +5341,16 @@
       <c r="CC54" s="10"/>
       <c r="CD54" s="10"/>
       <c r="CE54" s="10"/>
-      <c r="CF54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="10"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E55" s="12"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D55" s="12"/>
+      <c r="E55" s="10"/>
       <c r="F55" s="10"/>
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
@@ -5488,17 +5429,16 @@
       <c r="CC55" s="10"/>
       <c r="CD55" s="10"/>
       <c r="CE55" s="10"/>
-      <c r="CF55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E56" s="12"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D56" s="12"/>
+      <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
@@ -5577,17 +5517,16 @@
       <c r="CC56" s="10"/>
       <c r="CD56" s="10"/>
       <c r="CE56" s="10"/>
-      <c r="CF56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E57" s="12"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D57" s="12"/>
+      <c r="E57" s="10"/>
       <c r="F57" s="10"/>
       <c r="G57" s="10"/>
       <c r="H57" s="10"/>
@@ -5666,17 +5605,16 @@
       <c r="CC57" s="10"/>
       <c r="CD57" s="10"/>
       <c r="CE57" s="10"/>
-      <c r="CF57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="10"/>
-      <c r="B58" s="10"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E58" s="12"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D58" s="12"/>
+      <c r="E58" s="10"/>
       <c r="F58" s="10"/>
       <c r="G58" s="10"/>
       <c r="H58" s="10"/>
@@ -5755,17 +5693,16 @@
       <c r="CC58" s="10"/>
       <c r="CD58" s="10"/>
       <c r="CE58" s="10"/>
-      <c r="CF58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E59" s="12"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D59" s="12"/>
+      <c r="E59" s="10"/>
       <c r="F59" s="10"/>
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
@@ -5844,17 +5781,16 @@
       <c r="CC59" s="10"/>
       <c r="CD59" s="10"/>
       <c r="CE59" s="10"/>
-      <c r="CF59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="10"/>
-      <c r="B60" s="10"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E60" s="12"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D60" s="12"/>
+      <c r="E60" s="10"/>
       <c r="F60" s="10"/>
       <c r="G60" s="10"/>
       <c r="H60" s="10"/>
@@ -5933,17 +5869,16 @@
       <c r="CC60" s="10"/>
       <c r="CD60" s="10"/>
       <c r="CE60" s="10"/>
-      <c r="CF60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="10"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E61" s="12"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D61" s="12"/>
+      <c r="E61" s="10"/>
       <c r="F61" s="10"/>
       <c r="G61" s="10"/>
       <c r="H61" s="10"/>
@@ -6022,17 +5957,16 @@
       <c r="CC61" s="10"/>
       <c r="CD61" s="10"/>
       <c r="CE61" s="10"/>
-      <c r="CF61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="10"/>
-      <c r="B62" s="10"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E62" s="12"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D62" s="12"/>
+      <c r="E62" s="10"/>
       <c r="F62" s="10"/>
       <c r="G62" s="10"/>
       <c r="H62" s="10"/>
@@ -6111,17 +6045,16 @@
       <c r="CC62" s="10"/>
       <c r="CD62" s="10"/>
       <c r="CE62" s="10"/>
-      <c r="CF62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E63" s="12"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D63" s="12"/>
+      <c r="E63" s="10"/>
       <c r="F63" s="10"/>
       <c r="G63" s="10"/>
       <c r="H63" s="10"/>
@@ -6200,17 +6133,16 @@
       <c r="CC63" s="10"/>
       <c r="CD63" s="10"/>
       <c r="CE63" s="10"/>
-      <c r="CF63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="10"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E64" s="12"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D64" s="12"/>
+      <c r="E64" s="10"/>
       <c r="F64" s="10"/>
       <c r="G64" s="10"/>
       <c r="H64" s="10"/>
@@ -6289,17 +6221,16 @@
       <c r="CC64" s="10"/>
       <c r="CD64" s="10"/>
       <c r="CE64" s="10"/>
-      <c r="CF64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E65" s="12"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D65" s="12"/>
+      <c r="E65" s="10"/>
       <c r="F65" s="10"/>
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
@@ -6378,17 +6309,16 @@
       <c r="CC65" s="10"/>
       <c r="CD65" s="10"/>
       <c r="CE65" s="10"/>
-      <c r="CF65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="10"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E66" s="12"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D66" s="12"/>
+      <c r="E66" s="10"/>
       <c r="F66" s="10"/>
       <c r="G66" s="10"/>
       <c r="H66" s="10"/>
@@ -6467,17 +6397,16 @@
       <c r="CC66" s="10"/>
       <c r="CD66" s="10"/>
       <c r="CE66" s="10"/>
-      <c r="CF66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E67" s="12"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D67" s="12"/>
+      <c r="E67" s="10"/>
       <c r="F67" s="10"/>
       <c r="G67" s="10"/>
       <c r="H67" s="10"/>
@@ -6556,17 +6485,16 @@
       <c r="CC67" s="10"/>
       <c r="CD67" s="10"/>
       <c r="CE67" s="10"/>
-      <c r="CF67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="10"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E68" s="12"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D68" s="12"/>
+      <c r="E68" s="10"/>
       <c r="F68" s="10"/>
       <c r="G68" s="10"/>
       <c r="H68" s="10"/>
@@ -6645,17 +6573,16 @@
       <c r="CC68" s="10"/>
       <c r="CD68" s="10"/>
       <c r="CE68" s="10"/>
-      <c r="CF68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E69" s="12"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D69" s="12"/>
+      <c r="E69" s="10"/>
       <c r="F69" s="10"/>
       <c r="G69" s="10"/>
       <c r="H69" s="10"/>
@@ -6734,17 +6661,16 @@
       <c r="CC69" s="10"/>
       <c r="CD69" s="10"/>
       <c r="CE69" s="10"/>
-      <c r="CF69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="10"/>
-      <c r="B70" s="10"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E70" s="12"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D70" s="12"/>
+      <c r="E70" s="10"/>
       <c r="F70" s="10"/>
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
@@ -6823,17 +6749,16 @@
       <c r="CC70" s="10"/>
       <c r="CD70" s="10"/>
       <c r="CE70" s="10"/>
-      <c r="CF70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
-      <c r="B71" s="10"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E71" s="12"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D71" s="12"/>
+      <c r="E71" s="10"/>
       <c r="F71" s="10"/>
       <c r="G71" s="10"/>
       <c r="H71" s="10"/>
@@ -6912,17 +6837,16 @@
       <c r="CC71" s="10"/>
       <c r="CD71" s="10"/>
       <c r="CE71" s="10"/>
-      <c r="CF71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="10"/>
-      <c r="B72" s="10"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E72" s="12"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D72" s="12"/>
+      <c r="E72" s="10"/>
       <c r="F72" s="10"/>
       <c r="G72" s="10"/>
       <c r="H72" s="10"/>
@@ -7001,17 +6925,16 @@
       <c r="CC72" s="10"/>
       <c r="CD72" s="10"/>
       <c r="CE72" s="10"/>
-      <c r="CF72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
-      <c r="B73" s="10"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E73" s="12"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D73" s="12"/>
+      <c r="E73" s="10"/>
       <c r="F73" s="10"/>
       <c r="G73" s="10"/>
       <c r="H73" s="10"/>
@@ -7090,17 +7013,16 @@
       <c r="CC73" s="10"/>
       <c r="CD73" s="10"/>
       <c r="CE73" s="10"/>
-      <c r="CF73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="10"/>
-      <c r="B74" s="10"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E74" s="12"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D74" s="12"/>
+      <c r="E74" s="10"/>
       <c r="F74" s="10"/>
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
@@ -7179,17 +7101,16 @@
       <c r="CC74" s="10"/>
       <c r="CD74" s="10"/>
       <c r="CE74" s="10"/>
-      <c r="CF74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
-      <c r="B75" s="10"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E75" s="12"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D75" s="12"/>
+      <c r="E75" s="10"/>
       <c r="F75" s="10"/>
       <c r="G75" s="10"/>
       <c r="H75" s="10"/>
@@ -7268,17 +7189,16 @@
       <c r="CC75" s="10"/>
       <c r="CD75" s="10"/>
       <c r="CE75" s="10"/>
-      <c r="CF75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="10"/>
-      <c r="B76" s="10"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E76" s="12"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D76" s="12"/>
+      <c r="E76" s="10"/>
       <c r="F76" s="10"/>
       <c r="G76" s="10"/>
       <c r="H76" s="10"/>
@@ -7357,17 +7277,16 @@
       <c r="CC76" s="10"/>
       <c r="CD76" s="10"/>
       <c r="CE76" s="10"/>
-      <c r="CF76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="10"/>
-      <c r="B77" s="10"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E77" s="12"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D77" s="12"/>
+      <c r="E77" s="10"/>
       <c r="F77" s="10"/>
       <c r="G77" s="10"/>
       <c r="H77" s="10"/>
@@ -7446,17 +7365,16 @@
       <c r="CC77" s="10"/>
       <c r="CD77" s="10"/>
       <c r="CE77" s="10"/>
-      <c r="CF77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="10"/>
-      <c r="B78" s="10"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E78" s="12"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D78" s="12"/>
+      <c r="E78" s="10"/>
       <c r="F78" s="10"/>
       <c r="G78" s="10"/>
       <c r="H78" s="10"/>
@@ -7535,17 +7453,16 @@
       <c r="CC78" s="10"/>
       <c r="CD78" s="10"/>
       <c r="CE78" s="10"/>
-      <c r="CF78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="10"/>
-      <c r="B79" s="10"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E79" s="12"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D79" s="12"/>
+      <c r="E79" s="10"/>
       <c r="F79" s="10"/>
       <c r="G79" s="10"/>
       <c r="H79" s="10"/>
@@ -7624,17 +7541,16 @@
       <c r="CC79" s="10"/>
       <c r="CD79" s="10"/>
       <c r="CE79" s="10"/>
-      <c r="CF79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="10"/>
-      <c r="B80" s="10"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E80" s="12"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D80" s="12"/>
+      <c r="E80" s="10"/>
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
       <c r="H80" s="10"/>
@@ -7713,17 +7629,16 @@
       <c r="CC80" s="10"/>
       <c r="CD80" s="10"/>
       <c r="CE80" s="10"/>
-      <c r="CF80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="10"/>
-      <c r="B81" s="10"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E81" s="12"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D81" s="12"/>
+      <c r="E81" s="10"/>
       <c r="F81" s="10"/>
       <c r="G81" s="10"/>
       <c r="H81" s="10"/>
@@ -7802,17 +7717,16 @@
       <c r="CC81" s="10"/>
       <c r="CD81" s="10"/>
       <c r="CE81" s="10"/>
-      <c r="CF81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="10"/>
-      <c r="B82" s="10"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E82" s="12"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D82" s="12"/>
+      <c r="E82" s="10"/>
       <c r="F82" s="10"/>
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
@@ -7891,17 +7805,16 @@
       <c r="CC82" s="10"/>
       <c r="CD82" s="10"/>
       <c r="CE82" s="10"/>
-      <c r="CF82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="10"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E83" s="12"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D83" s="12"/>
+      <c r="E83" s="10"/>
       <c r="F83" s="10"/>
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
@@ -7980,17 +7893,16 @@
       <c r="CC83" s="10"/>
       <c r="CD83" s="10"/>
       <c r="CE83" s="10"/>
-      <c r="CF83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="10"/>
-      <c r="B84" s="10"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E84" s="12"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D84" s="12"/>
+      <c r="E84" s="10"/>
       <c r="F84" s="10"/>
       <c r="G84" s="10"/>
       <c r="H84" s="10"/>
@@ -8069,17 +7981,16 @@
       <c r="CC84" s="10"/>
       <c r="CD84" s="10"/>
       <c r="CE84" s="10"/>
-      <c r="CF84" s="10"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="10"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E85" s="12"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D85" s="12"/>
+      <c r="E85" s="10"/>
       <c r="F85" s="10"/>
       <c r="G85" s="10"/>
       <c r="H85" s="10"/>
@@ -8158,17 +8069,16 @@
       <c r="CC85" s="10"/>
       <c r="CD85" s="10"/>
       <c r="CE85" s="10"/>
-      <c r="CF85" s="10"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="10"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E86" s="12"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D86" s="12"/>
+      <c r="E86" s="10"/>
       <c r="F86" s="10"/>
       <c r="G86" s="10"/>
       <c r="H86" s="10"/>
@@ -8247,17 +8157,16 @@
       <c r="CC86" s="10"/>
       <c r="CD86" s="10"/>
       <c r="CE86" s="10"/>
-      <c r="CF86" s="10"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="10"/>
-      <c r="B87" s="10"/>
-      <c r="C87" s="14"/>
-      <c r="D87" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E87" s="12"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D87" s="12"/>
+      <c r="E87" s="10"/>
       <c r="F87" s="10"/>
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
@@ -8336,17 +8245,16 @@
       <c r="CC87" s="10"/>
       <c r="CD87" s="10"/>
       <c r="CE87" s="10"/>
-      <c r="CF87" s="10"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="14"/>
-      <c r="D88" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E88" s="12"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D88" s="12"/>
+      <c r="E88" s="10"/>
       <c r="F88" s="10"/>
       <c r="G88" s="10"/>
       <c r="H88" s="10"/>
@@ -8425,17 +8333,16 @@
       <c r="CC88" s="10"/>
       <c r="CD88" s="10"/>
       <c r="CE88" s="10"/>
-      <c r="CF88" s="10"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="10"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="14"/>
-      <c r="D89" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E89" s="12"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D89" s="12"/>
+      <c r="E89" s="10"/>
       <c r="F89" s="10"/>
       <c r="G89" s="10"/>
       <c r="H89" s="10"/>
@@ -8514,17 +8421,16 @@
       <c r="CC89" s="10"/>
       <c r="CD89" s="10"/>
       <c r="CE89" s="10"/>
-      <c r="CF89" s="10"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="10"/>
-      <c r="B90" s="10"/>
-      <c r="C90" s="14"/>
-      <c r="D90" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E90" s="12"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D90" s="12"/>
+      <c r="E90" s="10"/>
       <c r="F90" s="10"/>
       <c r="G90" s="10"/>
       <c r="H90" s="10"/>
@@ -8603,17 +8509,16 @@
       <c r="CC90" s="10"/>
       <c r="CD90" s="10"/>
       <c r="CE90" s="10"/>
-      <c r="CF90" s="10"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="10"/>
-      <c r="B91" s="10"/>
-      <c r="C91" s="14"/>
-      <c r="D91" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E91" s="12"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D91" s="12"/>
+      <c r="E91" s="10"/>
       <c r="F91" s="10"/>
       <c r="G91" s="10"/>
       <c r="H91" s="10"/>
@@ -8692,17 +8597,16 @@
       <c r="CC91" s="10"/>
       <c r="CD91" s="10"/>
       <c r="CE91" s="10"/>
-      <c r="CF91" s="10"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="10"/>
-      <c r="B92" s="10"/>
-      <c r="C92" s="14"/>
-      <c r="D92" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E92" s="12"/>
+      <c r="B92" s="14"/>
+      <c r="C92" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D92" s="12"/>
+      <c r="E92" s="10"/>
       <c r="F92" s="10"/>
       <c r="G92" s="10"/>
       <c r="H92" s="10"/>
@@ -8781,17 +8685,16 @@
       <c r="CC92" s="10"/>
       <c r="CD92" s="10"/>
       <c r="CE92" s="10"/>
-      <c r="CF92" s="10"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="10"/>
-      <c r="B93" s="10"/>
-      <c r="C93" s="14"/>
-      <c r="D93" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E93" s="12"/>
+      <c r="B93" s="14"/>
+      <c r="C93" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D93" s="12"/>
+      <c r="E93" s="10"/>
       <c r="F93" s="10"/>
       <c r="G93" s="10"/>
       <c r="H93" s="10"/>
@@ -8870,17 +8773,16 @@
       <c r="CC93" s="10"/>
       <c r="CD93" s="10"/>
       <c r="CE93" s="10"/>
-      <c r="CF93" s="10"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="10"/>
-      <c r="B94" s="10"/>
-      <c r="C94" s="14"/>
-      <c r="D94" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E94" s="12"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D94" s="12"/>
+      <c r="E94" s="10"/>
       <c r="F94" s="10"/>
       <c r="G94" s="10"/>
       <c r="H94" s="10"/>
@@ -8959,17 +8861,16 @@
       <c r="CC94" s="10"/>
       <c r="CD94" s="10"/>
       <c r="CE94" s="10"/>
-      <c r="CF94" s="10"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="10"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="14"/>
-      <c r="D95" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E95" s="12"/>
+      <c r="B95" s="14"/>
+      <c r="C95" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D95" s="12"/>
+      <c r="E95" s="10"/>
       <c r="F95" s="10"/>
       <c r="G95" s="10"/>
       <c r="H95" s="10"/>
@@ -9048,17 +8949,16 @@
       <c r="CC95" s="10"/>
       <c r="CD95" s="10"/>
       <c r="CE95" s="10"/>
-      <c r="CF95" s="10"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="10"/>
-      <c r="B96" s="10"/>
-      <c r="C96" s="14"/>
-      <c r="D96" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E96" s="12"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D96" s="12"/>
+      <c r="E96" s="10"/>
       <c r="F96" s="10"/>
       <c r="G96" s="10"/>
       <c r="H96" s="10"/>
@@ -9137,17 +9037,16 @@
       <c r="CC96" s="10"/>
       <c r="CD96" s="10"/>
       <c r="CE96" s="10"/>
-      <c r="CF96" s="10"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="10"/>
-      <c r="B97" s="10"/>
-      <c r="C97" s="14"/>
-      <c r="D97" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E97" s="12"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D97" s="12"/>
+      <c r="E97" s="10"/>
       <c r="F97" s="10"/>
       <c r="G97" s="10"/>
       <c r="H97" s="10"/>
@@ -9226,17 +9125,16 @@
       <c r="CC97" s="10"/>
       <c r="CD97" s="10"/>
       <c r="CE97" s="10"/>
-      <c r="CF97" s="10"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="10"/>
-      <c r="B98" s="10"/>
-      <c r="C98" s="14"/>
-      <c r="D98" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E98" s="12"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D98" s="12"/>
+      <c r="E98" s="10"/>
       <c r="F98" s="10"/>
       <c r="G98" s="10"/>
       <c r="H98" s="10"/>
@@ -9315,17 +9213,16 @@
       <c r="CC98" s="10"/>
       <c r="CD98" s="10"/>
       <c r="CE98" s="10"/>
-      <c r="CF98" s="10"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="10"/>
-      <c r="B99" s="10"/>
-      <c r="C99" s="14"/>
-      <c r="D99" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E99" s="12"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D99" s="12"/>
+      <c r="E99" s="10"/>
       <c r="F99" s="10"/>
       <c r="G99" s="10"/>
       <c r="H99" s="10"/>
@@ -9404,17 +9301,16 @@
       <c r="CC99" s="10"/>
       <c r="CD99" s="10"/>
       <c r="CE99" s="10"/>
-      <c r="CF99" s="10"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="10"/>
-      <c r="B100" s="10"/>
-      <c r="C100" s="14"/>
-      <c r="D100" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E100" s="12"/>
+      <c r="B100" s="14"/>
+      <c r="C100" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D100" s="12"/>
+      <c r="E100" s="10"/>
       <c r="F100" s="10"/>
       <c r="G100" s="10"/>
       <c r="H100" s="10"/>
@@ -9493,17 +9389,16 @@
       <c r="CC100" s="10"/>
       <c r="CD100" s="10"/>
       <c r="CE100" s="10"/>
-      <c r="CF100" s="10"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="10"/>
-      <c r="B101" s="10"/>
-      <c r="C101" s="14"/>
-      <c r="D101" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E101" s="12"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D101" s="12"/>
+      <c r="E101" s="10"/>
       <c r="F101" s="10"/>
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
@@ -9582,17 +9477,16 @@
       <c r="CC101" s="10"/>
       <c r="CD101" s="10"/>
       <c r="CE101" s="10"/>
-      <c r="CF101" s="10"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="10"/>
-      <c r="B102" s="10"/>
-      <c r="C102" s="14"/>
-      <c r="D102" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E102" s="12"/>
+      <c r="B102" s="14"/>
+      <c r="C102" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D102" s="12"/>
+      <c r="E102" s="10"/>
       <c r="F102" s="10"/>
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
@@ -9671,17 +9565,16 @@
       <c r="CC102" s="10"/>
       <c r="CD102" s="10"/>
       <c r="CE102" s="10"/>
-      <c r="CF102" s="10"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="10"/>
-      <c r="B103" s="10"/>
-      <c r="C103" s="14"/>
-      <c r="D103" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E103" s="12"/>
+      <c r="B103" s="14"/>
+      <c r="C103" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D103" s="12"/>
+      <c r="E103" s="10"/>
       <c r="F103" s="10"/>
       <c r="G103" s="10"/>
       <c r="H103" s="10"/>
@@ -9760,17 +9653,16 @@
       <c r="CC103" s="10"/>
       <c r="CD103" s="10"/>
       <c r="CE103" s="10"/>
-      <c r="CF103" s="10"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="10"/>
-      <c r="B104" s="10"/>
-      <c r="C104" s="14"/>
-      <c r="D104" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E104" s="12"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D104" s="12"/>
+      <c r="E104" s="10"/>
       <c r="F104" s="10"/>
       <c r="G104" s="10"/>
       <c r="H104" s="10"/>
@@ -9849,17 +9741,16 @@
       <c r="CC104" s="10"/>
       <c r="CD104" s="10"/>
       <c r="CE104" s="10"/>
-      <c r="CF104" s="10"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="10"/>
-      <c r="B105" s="10"/>
-      <c r="C105" s="14"/>
-      <c r="D105" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E105" s="12"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D105" s="12"/>
+      <c r="E105" s="10"/>
       <c r="F105" s="10"/>
       <c r="G105" s="10"/>
       <c r="H105" s="10"/>
@@ -9938,17 +9829,16 @@
       <c r="CC105" s="10"/>
       <c r="CD105" s="10"/>
       <c r="CE105" s="10"/>
-      <c r="CF105" s="10"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
-      <c r="C106" s="14"/>
-      <c r="D106" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E106" s="12"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D106" s="12"/>
+      <c r="E106" s="10"/>
       <c r="F106" s="10"/>
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
@@ -10027,17 +9917,16 @@
       <c r="CC106" s="10"/>
       <c r="CD106" s="10"/>
       <c r="CE106" s="10"/>
-      <c r="CF106" s="10"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="10"/>
-      <c r="B107" s="10"/>
-      <c r="C107" s="14"/>
-      <c r="D107" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E107" s="12"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D107" s="12"/>
+      <c r="E107" s="10"/>
       <c r="F107" s="10"/>
       <c r="G107" s="10"/>
       <c r="H107" s="10"/>
@@ -10116,17 +10005,16 @@
       <c r="CC107" s="10"/>
       <c r="CD107" s="10"/>
       <c r="CE107" s="10"/>
-      <c r="CF107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="10"/>
-      <c r="B108" s="10"/>
-      <c r="C108" s="14"/>
-      <c r="D108" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E108" s="12"/>
+      <c r="B108" s="14"/>
+      <c r="C108" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D108" s="12"/>
+      <c r="E108" s="10"/>
       <c r="F108" s="10"/>
       <c r="G108" s="10"/>
       <c r="H108" s="10"/>
@@ -10205,17 +10093,16 @@
       <c r="CC108" s="10"/>
       <c r="CD108" s="10"/>
       <c r="CE108" s="10"/>
-      <c r="CF108" s="10"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="10"/>
-      <c r="B109" s="10"/>
-      <c r="C109" s="14"/>
-      <c r="D109" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E109" s="12"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D109" s="12"/>
+      <c r="E109" s="10"/>
       <c r="F109" s="10"/>
       <c r="G109" s="10"/>
       <c r="H109" s="10"/>
@@ -10294,17 +10181,16 @@
       <c r="CC109" s="10"/>
       <c r="CD109" s="10"/>
       <c r="CE109" s="10"/>
-      <c r="CF109" s="10"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="10"/>
-      <c r="B110" s="10"/>
-      <c r="C110" s="14"/>
-      <c r="D110" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E110" s="12"/>
+      <c r="B110" s="14"/>
+      <c r="C110" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D110" s="12"/>
+      <c r="E110" s="10"/>
       <c r="F110" s="10"/>
       <c r="G110" s="10"/>
       <c r="H110" s="10"/>
@@ -10383,17 +10269,16 @@
       <c r="CC110" s="10"/>
       <c r="CD110" s="10"/>
       <c r="CE110" s="10"/>
-      <c r="CF110" s="10"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="10"/>
-      <c r="B111" s="10"/>
-      <c r="C111" s="14"/>
-      <c r="D111" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E111" s="12"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D111" s="12"/>
+      <c r="E111" s="10"/>
       <c r="F111" s="10"/>
       <c r="G111" s="10"/>
       <c r="H111" s="10"/>
@@ -10472,17 +10357,16 @@
       <c r="CC111" s="10"/>
       <c r="CD111" s="10"/>
       <c r="CE111" s="10"/>
-      <c r="CF111" s="10"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="10"/>
-      <c r="B112" s="10"/>
-      <c r="C112" s="14"/>
-      <c r="D112" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E112" s="12"/>
+      <c r="B112" s="14"/>
+      <c r="C112" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D112" s="12"/>
+      <c r="E112" s="10"/>
       <c r="F112" s="10"/>
       <c r="G112" s="10"/>
       <c r="H112" s="10"/>
@@ -10561,17 +10445,16 @@
       <c r="CC112" s="10"/>
       <c r="CD112" s="10"/>
       <c r="CE112" s="10"/>
-      <c r="CF112" s="10"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="10"/>
-      <c r="B113" s="10"/>
-      <c r="C113" s="14"/>
-      <c r="D113" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E113" s="12"/>
+      <c r="B113" s="14"/>
+      <c r="C113" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D113" s="12"/>
+      <c r="E113" s="10"/>
       <c r="F113" s="10"/>
       <c r="G113" s="10"/>
       <c r="H113" s="10"/>
@@ -10650,17 +10533,16 @@
       <c r="CC113" s="10"/>
       <c r="CD113" s="10"/>
       <c r="CE113" s="10"/>
-      <c r="CF113" s="10"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="10"/>
-      <c r="B114" s="10"/>
-      <c r="C114" s="14"/>
-      <c r="D114" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E114" s="12"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D114" s="12"/>
+      <c r="E114" s="10"/>
       <c r="F114" s="10"/>
       <c r="G114" s="10"/>
       <c r="H114" s="10"/>
@@ -10739,17 +10621,16 @@
       <c r="CC114" s="10"/>
       <c r="CD114" s="10"/>
       <c r="CE114" s="10"/>
-      <c r="CF114" s="10"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="10"/>
-      <c r="B115" s="10"/>
-      <c r="C115" s="14"/>
-      <c r="D115" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E115" s="12"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D115" s="12"/>
+      <c r="E115" s="10"/>
       <c r="F115" s="10"/>
       <c r="G115" s="10"/>
       <c r="H115" s="10"/>
@@ -10828,17 +10709,16 @@
       <c r="CC115" s="10"/>
       <c r="CD115" s="10"/>
       <c r="CE115" s="10"/>
-      <c r="CF115" s="10"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="10"/>
-      <c r="B116" s="10"/>
-      <c r="C116" s="14"/>
-      <c r="D116" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E116" s="12"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D116" s="12"/>
+      <c r="E116" s="10"/>
       <c r="F116" s="10"/>
       <c r="G116" s="10"/>
       <c r="H116" s="10"/>
@@ -10917,17 +10797,16 @@
       <c r="CC116" s="10"/>
       <c r="CD116" s="10"/>
       <c r="CE116" s="10"/>
-      <c r="CF116" s="10"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="10"/>
-      <c r="B117" s="10"/>
-      <c r="C117" s="14"/>
-      <c r="D117" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E117" s="12"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D117" s="12"/>
+      <c r="E117" s="10"/>
       <c r="F117" s="10"/>
       <c r="G117" s="10"/>
       <c r="H117" s="10"/>
@@ -11006,17 +10885,16 @@
       <c r="CC117" s="10"/>
       <c r="CD117" s="10"/>
       <c r="CE117" s="10"/>
-      <c r="CF117" s="10"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="10"/>
-      <c r="B118" s="10"/>
-      <c r="C118" s="14"/>
-      <c r="D118" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E118" s="12"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D118" s="12"/>
+      <c r="E118" s="10"/>
       <c r="F118" s="10"/>
       <c r="G118" s="10"/>
       <c r="H118" s="10"/>
@@ -11095,17 +10973,16 @@
       <c r="CC118" s="10"/>
       <c r="CD118" s="10"/>
       <c r="CE118" s="10"/>
-      <c r="CF118" s="10"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="10"/>
-      <c r="B119" s="10"/>
-      <c r="C119" s="14"/>
-      <c r="D119" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E119" s="12"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D119" s="12"/>
+      <c r="E119" s="10"/>
       <c r="F119" s="10"/>
       <c r="G119" s="10"/>
       <c r="H119" s="10"/>
@@ -11184,17 +11061,16 @@
       <c r="CC119" s="10"/>
       <c r="CD119" s="10"/>
       <c r="CE119" s="10"/>
-      <c r="CF119" s="10"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="10"/>
-      <c r="B120" s="10"/>
-      <c r="C120" s="14"/>
-      <c r="D120" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E120" s="12"/>
+      <c r="B120" s="14"/>
+      <c r="C120" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D120" s="12"/>
+      <c r="E120" s="10"/>
       <c r="F120" s="10"/>
       <c r="G120" s="10"/>
       <c r="H120" s="10"/>
@@ -11273,17 +11149,16 @@
       <c r="CC120" s="10"/>
       <c r="CD120" s="10"/>
       <c r="CE120" s="10"/>
-      <c r="CF120" s="10"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="10"/>
-      <c r="B121" s="10"/>
-      <c r="C121" s="14"/>
-      <c r="D121" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E121" s="12"/>
+      <c r="B121" s="14"/>
+      <c r="C121" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D121" s="12"/>
+      <c r="E121" s="10"/>
       <c r="F121" s="10"/>
       <c r="G121" s="10"/>
       <c r="H121" s="10"/>
@@ -11362,17 +11237,16 @@
       <c r="CC121" s="10"/>
       <c r="CD121" s="10"/>
       <c r="CE121" s="10"/>
-      <c r="CF121" s="10"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="10"/>
-      <c r="B122" s="10"/>
-      <c r="C122" s="14"/>
-      <c r="D122" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E122" s="12"/>
+      <c r="B122" s="14"/>
+      <c r="C122" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D122" s="12"/>
+      <c r="E122" s="10"/>
       <c r="F122" s="10"/>
       <c r="G122" s="10"/>
       <c r="H122" s="10"/>
@@ -11451,17 +11325,16 @@
       <c r="CC122" s="10"/>
       <c r="CD122" s="10"/>
       <c r="CE122" s="10"/>
-      <c r="CF122" s="10"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="10"/>
-      <c r="B123" s="10"/>
-      <c r="C123" s="14"/>
-      <c r="D123" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E123" s="12"/>
+      <c r="B123" s="14"/>
+      <c r="C123" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D123" s="12"/>
+      <c r="E123" s="10"/>
       <c r="F123" s="10"/>
       <c r="G123" s="10"/>
       <c r="H123" s="10"/>
@@ -11540,17 +11413,16 @@
       <c r="CC123" s="10"/>
       <c r="CD123" s="10"/>
       <c r="CE123" s="10"/>
-      <c r="CF123" s="10"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="10"/>
-      <c r="B124" s="10"/>
-      <c r="C124" s="14"/>
-      <c r="D124" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E124" s="12"/>
+      <c r="B124" s="14"/>
+      <c r="C124" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D124" s="12"/>
+      <c r="E124" s="10"/>
       <c r="F124" s="10"/>
       <c r="G124" s="10"/>
       <c r="H124" s="10"/>
@@ -11629,17 +11501,16 @@
       <c r="CC124" s="10"/>
       <c r="CD124" s="10"/>
       <c r="CE124" s="10"/>
-      <c r="CF124" s="10"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="10"/>
-      <c r="B125" s="10"/>
-      <c r="C125" s="14"/>
-      <c r="D125" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E125" s="12"/>
+      <c r="B125" s="14"/>
+      <c r="C125" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D125" s="12"/>
+      <c r="E125" s="10"/>
       <c r="F125" s="10"/>
       <c r="G125" s="10"/>
       <c r="H125" s="10"/>
@@ -11718,17 +11589,16 @@
       <c r="CC125" s="10"/>
       <c r="CD125" s="10"/>
       <c r="CE125" s="10"/>
-      <c r="CF125" s="10"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="10"/>
-      <c r="B126" s="10"/>
-      <c r="C126" s="14"/>
-      <c r="D126" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E126" s="12"/>
+      <c r="B126" s="14"/>
+      <c r="C126" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D126" s="12"/>
+      <c r="E126" s="10"/>
       <c r="F126" s="10"/>
       <c r="G126" s="10"/>
       <c r="H126" s="10"/>
@@ -11807,17 +11677,16 @@
       <c r="CC126" s="10"/>
       <c r="CD126" s="10"/>
       <c r="CE126" s="10"/>
-      <c r="CF126" s="10"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="10"/>
-      <c r="B127" s="10"/>
-      <c r="C127" s="14"/>
-      <c r="D127" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E127" s="12"/>
+      <c r="B127" s="14"/>
+      <c r="C127" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D127" s="12"/>
+      <c r="E127" s="10"/>
       <c r="F127" s="10"/>
       <c r="G127" s="10"/>
       <c r="H127" s="10"/>
@@ -11896,17 +11765,16 @@
       <c r="CC127" s="10"/>
       <c r="CD127" s="10"/>
       <c r="CE127" s="10"/>
-      <c r="CF127" s="10"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="10"/>
-      <c r="B128" s="10"/>
-      <c r="C128" s="14"/>
-      <c r="D128" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E128" s="12"/>
+      <c r="B128" s="14"/>
+      <c r="C128" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D128" s="12"/>
+      <c r="E128" s="10"/>
       <c r="F128" s="10"/>
       <c r="G128" s="10"/>
       <c r="H128" s="10"/>
@@ -11985,17 +11853,16 @@
       <c r="CC128" s="10"/>
       <c r="CD128" s="10"/>
       <c r="CE128" s="10"/>
-      <c r="CF128" s="10"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="10"/>
-      <c r="B129" s="10"/>
-      <c r="C129" s="14"/>
-      <c r="D129" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E129" s="12"/>
+      <c r="B129" s="14"/>
+      <c r="C129" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D129" s="12"/>
+      <c r="E129" s="10"/>
       <c r="F129" s="10"/>
       <c r="G129" s="10"/>
       <c r="H129" s="10"/>
@@ -12074,17 +11941,16 @@
       <c r="CC129" s="10"/>
       <c r="CD129" s="10"/>
       <c r="CE129" s="10"/>
-      <c r="CF129" s="10"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="10"/>
-      <c r="B130" s="10"/>
-      <c r="C130" s="14"/>
-      <c r="D130" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E130" s="12"/>
+      <c r="B130" s="14"/>
+      <c r="C130" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D130" s="12"/>
+      <c r="E130" s="10"/>
       <c r="F130" s="10"/>
       <c r="G130" s="10"/>
       <c r="H130" s="10"/>
@@ -12163,17 +12029,16 @@
       <c r="CC130" s="10"/>
       <c r="CD130" s="10"/>
       <c r="CE130" s="10"/>
-      <c r="CF130" s="10"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="10"/>
-      <c r="B131" s="10"/>
-      <c r="C131" s="14"/>
-      <c r="D131" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E131" s="12"/>
+      <c r="B131" s="14"/>
+      <c r="C131" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D131" s="12"/>
+      <c r="E131" s="10"/>
       <c r="F131" s="10"/>
       <c r="G131" s="10"/>
       <c r="H131" s="10"/>
@@ -12252,17 +12117,16 @@
       <c r="CC131" s="10"/>
       <c r="CD131" s="10"/>
       <c r="CE131" s="10"/>
-      <c r="CF131" s="10"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="10"/>
-      <c r="B132" s="10"/>
-      <c r="C132" s="14"/>
-      <c r="D132" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E132" s="12"/>
+      <c r="B132" s="14"/>
+      <c r="C132" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D132" s="12"/>
+      <c r="E132" s="10"/>
       <c r="F132" s="10"/>
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
@@ -12341,17 +12205,16 @@
       <c r="CC132" s="10"/>
       <c r="CD132" s="10"/>
       <c r="CE132" s="10"/>
-      <c r="CF132" s="10"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="10"/>
-      <c r="B133" s="10"/>
-      <c r="C133" s="14"/>
-      <c r="D133" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E133" s="12"/>
+      <c r="B133" s="14"/>
+      <c r="C133" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D133" s="12"/>
+      <c r="E133" s="10"/>
       <c r="F133" s="10"/>
       <c r="G133" s="10"/>
       <c r="H133" s="10"/>
@@ -12430,17 +12293,16 @@
       <c r="CC133" s="10"/>
       <c r="CD133" s="10"/>
       <c r="CE133" s="10"/>
-      <c r="CF133" s="10"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="10"/>
-      <c r="B134" s="10"/>
-      <c r="C134" s="14"/>
-      <c r="D134" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E134" s="12"/>
+      <c r="B134" s="14"/>
+      <c r="C134" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D134" s="12"/>
+      <c r="E134" s="10"/>
       <c r="F134" s="10"/>
       <c r="G134" s="10"/>
       <c r="H134" s="10"/>
@@ -12519,17 +12381,16 @@
       <c r="CC134" s="10"/>
       <c r="CD134" s="10"/>
       <c r="CE134" s="10"/>
-      <c r="CF134" s="10"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="10"/>
-      <c r="B135" s="10"/>
-      <c r="C135" s="14"/>
-      <c r="D135" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E135" s="12"/>
+      <c r="B135" s="14"/>
+      <c r="C135" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D135" s="12"/>
+      <c r="E135" s="10"/>
       <c r="F135" s="10"/>
       <c r="G135" s="10"/>
       <c r="H135" s="10"/>
@@ -12608,17 +12469,16 @@
       <c r="CC135" s="10"/>
       <c r="CD135" s="10"/>
       <c r="CE135" s="10"/>
-      <c r="CF135" s="10"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="10"/>
-      <c r="B136" s="10"/>
-      <c r="C136" s="14"/>
-      <c r="D136" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E136" s="12"/>
+      <c r="B136" s="14"/>
+      <c r="C136" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D136" s="12"/>
+      <c r="E136" s="10"/>
       <c r="F136" s="10"/>
       <c r="G136" s="10"/>
       <c r="H136" s="10"/>
@@ -12697,17 +12557,16 @@
       <c r="CC136" s="10"/>
       <c r="CD136" s="10"/>
       <c r="CE136" s="10"/>
-      <c r="CF136" s="10"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="10"/>
-      <c r="B137" s="10"/>
-      <c r="C137" s="14"/>
-      <c r="D137" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E137" s="12"/>
+      <c r="B137" s="14"/>
+      <c r="C137" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D137" s="12"/>
+      <c r="E137" s="10"/>
       <c r="F137" s="10"/>
       <c r="G137" s="10"/>
       <c r="H137" s="10"/>
@@ -12786,17 +12645,16 @@
       <c r="CC137" s="10"/>
       <c r="CD137" s="10"/>
       <c r="CE137" s="10"/>
-      <c r="CF137" s="10"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="10"/>
-      <c r="B138" s="10"/>
-      <c r="C138" s="14"/>
-      <c r="D138" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E138" s="12"/>
+      <c r="B138" s="14"/>
+      <c r="C138" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D138" s="12"/>
+      <c r="E138" s="10"/>
       <c r="F138" s="10"/>
       <c r="G138" s="10"/>
       <c r="H138" s="10"/>
@@ -12875,17 +12733,16 @@
       <c r="CC138" s="10"/>
       <c r="CD138" s="10"/>
       <c r="CE138" s="10"/>
-      <c r="CF138" s="10"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="10"/>
-      <c r="B139" s="10"/>
-      <c r="C139" s="14"/>
-      <c r="D139" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E139" s="12"/>
+      <c r="B139" s="14"/>
+      <c r="C139" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D139" s="12"/>
+      <c r="E139" s="10"/>
       <c r="F139" s="10"/>
       <c r="G139" s="10"/>
       <c r="H139" s="10"/>
@@ -12964,17 +12821,16 @@
       <c r="CC139" s="10"/>
       <c r="CD139" s="10"/>
       <c r="CE139" s="10"/>
-      <c r="CF139" s="10"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="10"/>
-      <c r="B140" s="10"/>
-      <c r="C140" s="14"/>
-      <c r="D140" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E140" s="12"/>
+      <c r="B140" s="14"/>
+      <c r="C140" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D140" s="12"/>
+      <c r="E140" s="10"/>
       <c r="F140" s="10"/>
       <c r="G140" s="10"/>
       <c r="H140" s="10"/>
@@ -13053,17 +12909,16 @@
       <c r="CC140" s="10"/>
       <c r="CD140" s="10"/>
       <c r="CE140" s="10"/>
-      <c r="CF140" s="10"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="10"/>
-      <c r="B141" s="10"/>
-      <c r="C141" s="14"/>
-      <c r="D141" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E141" s="12"/>
+      <c r="B141" s="14"/>
+      <c r="C141" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D141" s="12"/>
+      <c r="E141" s="10"/>
       <c r="F141" s="10"/>
       <c r="G141" s="10"/>
       <c r="H141" s="10"/>
@@ -13142,17 +12997,16 @@
       <c r="CC141" s="10"/>
       <c r="CD141" s="10"/>
       <c r="CE141" s="10"/>
-      <c r="CF141" s="10"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="10"/>
-      <c r="B142" s="10"/>
-      <c r="C142" s="14"/>
-      <c r="D142" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E142" s="12"/>
+      <c r="B142" s="14"/>
+      <c r="C142" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D142" s="12"/>
+      <c r="E142" s="10"/>
       <c r="F142" s="10"/>
       <c r="G142" s="10"/>
       <c r="H142" s="10"/>
@@ -13231,17 +13085,16 @@
       <c r="CC142" s="10"/>
       <c r="CD142" s="10"/>
       <c r="CE142" s="10"/>
-      <c r="CF142" s="10"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="10"/>
-      <c r="B143" s="10"/>
-      <c r="C143" s="14"/>
-      <c r="D143" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E143" s="12"/>
+      <c r="B143" s="14"/>
+      <c r="C143" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D143" s="12"/>
+      <c r="E143" s="10"/>
       <c r="F143" s="10"/>
       <c r="G143" s="10"/>
       <c r="H143" s="10"/>
@@ -13320,17 +13173,16 @@
       <c r="CC143" s="10"/>
       <c r="CD143" s="10"/>
       <c r="CE143" s="10"/>
-      <c r="CF143" s="10"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="10"/>
-      <c r="B144" s="10"/>
-      <c r="C144" s="14"/>
-      <c r="D144" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E144" s="12"/>
+      <c r="B144" s="14"/>
+      <c r="C144" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D144" s="12"/>
+      <c r="E144" s="10"/>
       <c r="F144" s="10"/>
       <c r="G144" s="10"/>
       <c r="H144" s="10"/>
@@ -13409,17 +13261,16 @@
       <c r="CC144" s="10"/>
       <c r="CD144" s="10"/>
       <c r="CE144" s="10"/>
-      <c r="CF144" s="10"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="10"/>
-      <c r="B145" s="10"/>
-      <c r="C145" s="14"/>
-      <c r="D145" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E145" s="12"/>
+      <c r="B145" s="14"/>
+      <c r="C145" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D145" s="12"/>
+      <c r="E145" s="10"/>
       <c r="F145" s="10"/>
       <c r="G145" s="10"/>
       <c r="H145" s="10"/>
@@ -13498,17 +13349,16 @@
       <c r="CC145" s="10"/>
       <c r="CD145" s="10"/>
       <c r="CE145" s="10"/>
-      <c r="CF145" s="10"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="10"/>
-      <c r="B146" s="10"/>
-      <c r="C146" s="14"/>
-      <c r="D146" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E146" s="12"/>
+      <c r="B146" s="14"/>
+      <c r="C146" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D146" s="12"/>
+      <c r="E146" s="10"/>
       <c r="F146" s="10"/>
       <c r="G146" s="10"/>
       <c r="H146" s="10"/>
@@ -13587,17 +13437,16 @@
       <c r="CC146" s="10"/>
       <c r="CD146" s="10"/>
       <c r="CE146" s="10"/>
-      <c r="CF146" s="10"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="10"/>
-      <c r="B147" s="10"/>
-      <c r="C147" s="14"/>
-      <c r="D147" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E147" s="12"/>
+      <c r="B147" s="14"/>
+      <c r="C147" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D147" s="12"/>
+      <c r="E147" s="10"/>
       <c r="F147" s="10"/>
       <c r="G147" s="10"/>
       <c r="H147" s="10"/>
@@ -13676,17 +13525,16 @@
       <c r="CC147" s="10"/>
       <c r="CD147" s="10"/>
       <c r="CE147" s="10"/>
-      <c r="CF147" s="10"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="10"/>
-      <c r="B148" s="10"/>
-      <c r="C148" s="14"/>
-      <c r="D148" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E148" s="12"/>
+      <c r="B148" s="14"/>
+      <c r="C148" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D148" s="12"/>
+      <c r="E148" s="10"/>
       <c r="F148" s="10"/>
       <c r="G148" s="10"/>
       <c r="H148" s="10"/>
@@ -13765,17 +13613,16 @@
       <c r="CC148" s="10"/>
       <c r="CD148" s="10"/>
       <c r="CE148" s="10"/>
-      <c r="CF148" s="10"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="10"/>
-      <c r="B149" s="10"/>
-      <c r="C149" s="14"/>
-      <c r="D149" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E149" s="12"/>
+      <c r="B149" s="14"/>
+      <c r="C149" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D149" s="12"/>
+      <c r="E149" s="10"/>
       <c r="F149" s="10"/>
       <c r="G149" s="10"/>
       <c r="H149" s="10"/>
@@ -13854,17 +13701,16 @@
       <c r="CC149" s="10"/>
       <c r="CD149" s="10"/>
       <c r="CE149" s="10"/>
-      <c r="CF149" s="10"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="10"/>
-      <c r="B150" s="10"/>
-      <c r="C150" s="14"/>
-      <c r="D150" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E150" s="12"/>
+      <c r="B150" s="14"/>
+      <c r="C150" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D150" s="12"/>
+      <c r="E150" s="10"/>
       <c r="F150" s="10"/>
       <c r="G150" s="10"/>
       <c r="H150" s="10"/>
@@ -13943,17 +13789,16 @@
       <c r="CC150" s="10"/>
       <c r="CD150" s="10"/>
       <c r="CE150" s="10"/>
-      <c r="CF150" s="10"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="10"/>
-      <c r="B151" s="10"/>
-      <c r="C151" s="14"/>
-      <c r="D151" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E151" s="12"/>
+      <c r="B151" s="14"/>
+      <c r="C151" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D151" s="12"/>
+      <c r="E151" s="10"/>
       <c r="F151" s="10"/>
       <c r="G151" s="10"/>
       <c r="H151" s="10"/>
@@ -14032,17 +13877,16 @@
       <c r="CC151" s="10"/>
       <c r="CD151" s="10"/>
       <c r="CE151" s="10"/>
-      <c r="CF151" s="10"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="10"/>
-      <c r="B152" s="10"/>
-      <c r="C152" s="14"/>
-      <c r="D152" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E152" s="12"/>
+      <c r="B152" s="14"/>
+      <c r="C152" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D152" s="12"/>
+      <c r="E152" s="10"/>
       <c r="F152" s="10"/>
       <c r="G152" s="10"/>
       <c r="H152" s="10"/>
@@ -14121,17 +13965,16 @@
       <c r="CC152" s="10"/>
       <c r="CD152" s="10"/>
       <c r="CE152" s="10"/>
-      <c r="CF152" s="10"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="10"/>
-      <c r="B153" s="10"/>
-      <c r="C153" s="14"/>
-      <c r="D153" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E153" s="12"/>
+      <c r="B153" s="14"/>
+      <c r="C153" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D153" s="12"/>
+      <c r="E153" s="10"/>
       <c r="F153" s="10"/>
       <c r="G153" s="10"/>
       <c r="H153" s="10"/>
@@ -14210,17 +14053,16 @@
       <c r="CC153" s="10"/>
       <c r="CD153" s="10"/>
       <c r="CE153" s="10"/>
-      <c r="CF153" s="10"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="10"/>
-      <c r="B154" s="10"/>
-      <c r="C154" s="14"/>
-      <c r="D154" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E154" s="12"/>
+      <c r="B154" s="14"/>
+      <c r="C154" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D154" s="12"/>
+      <c r="E154" s="10"/>
       <c r="F154" s="10"/>
       <c r="G154" s="10"/>
       <c r="H154" s="10"/>
@@ -14299,17 +14141,16 @@
       <c r="CC154" s="10"/>
       <c r="CD154" s="10"/>
       <c r="CE154" s="10"/>
-      <c r="CF154" s="10"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="10"/>
-      <c r="B155" s="10"/>
-      <c r="C155" s="14"/>
-      <c r="D155" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E155" s="12"/>
+      <c r="B155" s="14"/>
+      <c r="C155" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D155" s="12"/>
+      <c r="E155" s="10"/>
       <c r="F155" s="10"/>
       <c r="G155" s="10"/>
       <c r="H155" s="10"/>
@@ -14388,17 +14229,16 @@
       <c r="CC155" s="10"/>
       <c r="CD155" s="10"/>
       <c r="CE155" s="10"/>
-      <c r="CF155" s="10"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="10"/>
-      <c r="B156" s="10"/>
-      <c r="C156" s="14"/>
-      <c r="D156" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E156" s="12"/>
+      <c r="B156" s="14"/>
+      <c r="C156" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D156" s="12"/>
+      <c r="E156" s="10"/>
       <c r="F156" s="10"/>
       <c r="G156" s="10"/>
       <c r="H156" s="10"/>
@@ -14477,17 +14317,16 @@
       <c r="CC156" s="10"/>
       <c r="CD156" s="10"/>
       <c r="CE156" s="10"/>
-      <c r="CF156" s="10"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="10"/>
-      <c r="B157" s="10"/>
-      <c r="C157" s="14"/>
-      <c r="D157" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E157" s="12"/>
+      <c r="B157" s="14"/>
+      <c r="C157" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D157" s="12"/>
+      <c r="E157" s="10"/>
       <c r="F157" s="10"/>
       <c r="G157" s="10"/>
       <c r="H157" s="10"/>
@@ -14566,17 +14405,16 @@
       <c r="CC157" s="10"/>
       <c r="CD157" s="10"/>
       <c r="CE157" s="10"/>
-      <c r="CF157" s="10"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="10"/>
-      <c r="B158" s="10"/>
-      <c r="C158" s="14"/>
-      <c r="D158" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E158" s="12"/>
+      <c r="B158" s="14"/>
+      <c r="C158" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D158" s="12"/>
+      <c r="E158" s="10"/>
       <c r="F158" s="10"/>
       <c r="G158" s="10"/>
       <c r="H158" s="10"/>
@@ -14655,17 +14493,16 @@
       <c r="CC158" s="10"/>
       <c r="CD158" s="10"/>
       <c r="CE158" s="10"/>
-      <c r="CF158" s="10"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="10"/>
-      <c r="B159" s="10"/>
-      <c r="C159" s="14"/>
-      <c r="D159" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E159" s="12"/>
+      <c r="B159" s="14"/>
+      <c r="C159" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D159" s="12"/>
+      <c r="E159" s="10"/>
       <c r="F159" s="10"/>
       <c r="G159" s="10"/>
       <c r="H159" s="10"/>
@@ -14744,17 +14581,16 @@
       <c r="CC159" s="10"/>
       <c r="CD159" s="10"/>
       <c r="CE159" s="10"/>
-      <c r="CF159" s="10"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="10"/>
-      <c r="B160" s="10"/>
-      <c r="C160" s="14"/>
-      <c r="D160" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E160" s="12"/>
+      <c r="B160" s="14"/>
+      <c r="C160" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D160" s="12"/>
+      <c r="E160" s="10"/>
       <c r="F160" s="10"/>
       <c r="G160" s="10"/>
       <c r="H160" s="10"/>
@@ -14833,17 +14669,16 @@
       <c r="CC160" s="10"/>
       <c r="CD160" s="10"/>
       <c r="CE160" s="10"/>
-      <c r="CF160" s="10"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="10"/>
-      <c r="B161" s="10"/>
-      <c r="C161" s="14"/>
-      <c r="D161" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E161" s="12"/>
+      <c r="B161" s="14"/>
+      <c r="C161" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D161" s="12"/>
+      <c r="E161" s="10"/>
       <c r="F161" s="10"/>
       <c r="G161" s="10"/>
       <c r="H161" s="10"/>
@@ -14922,17 +14757,16 @@
       <c r="CC161" s="10"/>
       <c r="CD161" s="10"/>
       <c r="CE161" s="10"/>
-      <c r="CF161" s="10"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="10"/>
-      <c r="B162" s="10"/>
-      <c r="C162" s="14"/>
-      <c r="D162" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E162" s="12"/>
+      <c r="B162" s="14"/>
+      <c r="C162" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D162" s="12"/>
+      <c r="E162" s="10"/>
       <c r="F162" s="10"/>
       <c r="G162" s="10"/>
       <c r="H162" s="10"/>
@@ -15011,17 +14845,16 @@
       <c r="CC162" s="10"/>
       <c r="CD162" s="10"/>
       <c r="CE162" s="10"/>
-      <c r="CF162" s="10"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="10"/>
-      <c r="B163" s="10"/>
-      <c r="C163" s="14"/>
-      <c r="D163" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E163" s="12"/>
+      <c r="B163" s="14"/>
+      <c r="C163" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D163" s="12"/>
+      <c r="E163" s="10"/>
       <c r="F163" s="10"/>
       <c r="G163" s="10"/>
       <c r="H163" s="10"/>
@@ -15100,17 +14933,16 @@
       <c r="CC163" s="10"/>
       <c r="CD163" s="10"/>
       <c r="CE163" s="10"/>
-      <c r="CF163" s="10"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="10"/>
-      <c r="B164" s="10"/>
-      <c r="C164" s="14"/>
-      <c r="D164" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E164" s="12"/>
+      <c r="B164" s="14"/>
+      <c r="C164" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D164" s="12"/>
+      <c r="E164" s="10"/>
       <c r="F164" s="10"/>
       <c r="G164" s="10"/>
       <c r="H164" s="10"/>
@@ -15189,17 +15021,16 @@
       <c r="CC164" s="10"/>
       <c r="CD164" s="10"/>
       <c r="CE164" s="10"/>
-      <c r="CF164" s="10"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="10"/>
-      <c r="B165" s="10"/>
-      <c r="C165" s="14"/>
-      <c r="D165" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E165" s="12"/>
+      <c r="B165" s="14"/>
+      <c r="C165" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D165" s="12"/>
+      <c r="E165" s="10"/>
       <c r="F165" s="10"/>
       <c r="G165" s="10"/>
       <c r="H165" s="10"/>
@@ -15278,17 +15109,16 @@
       <c r="CC165" s="10"/>
       <c r="CD165" s="10"/>
       <c r="CE165" s="10"/>
-      <c r="CF165" s="10"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="10"/>
-      <c r="B166" s="10"/>
-      <c r="C166" s="14"/>
-      <c r="D166" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E166" s="12"/>
+      <c r="B166" s="14"/>
+      <c r="C166" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D166" s="12"/>
+      <c r="E166" s="10"/>
       <c r="F166" s="10"/>
       <c r="G166" s="10"/>
       <c r="H166" s="10"/>
@@ -15367,17 +15197,16 @@
       <c r="CC166" s="10"/>
       <c r="CD166" s="10"/>
       <c r="CE166" s="10"/>
-      <c r="CF166" s="10"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="10"/>
-      <c r="B167" s="10"/>
-      <c r="C167" s="14"/>
-      <c r="D167" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E167" s="12"/>
+      <c r="B167" s="14"/>
+      <c r="C167" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D167" s="12"/>
+      <c r="E167" s="10"/>
       <c r="F167" s="10"/>
       <c r="G167" s="10"/>
       <c r="H167" s="10"/>
@@ -15456,17 +15285,16 @@
       <c r="CC167" s="10"/>
       <c r="CD167" s="10"/>
       <c r="CE167" s="10"/>
-      <c r="CF167" s="10"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="10"/>
-      <c r="B168" s="10"/>
-      <c r="C168" s="14"/>
-      <c r="D168" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E168" s="12"/>
+      <c r="B168" s="14"/>
+      <c r="C168" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D168" s="12"/>
+      <c r="E168" s="10"/>
       <c r="F168" s="10"/>
       <c r="G168" s="10"/>
       <c r="H168" s="10"/>
@@ -15545,17 +15373,16 @@
       <c r="CC168" s="10"/>
       <c r="CD168" s="10"/>
       <c r="CE168" s="10"/>
-      <c r="CF168" s="10"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="10"/>
-      <c r="B169" s="10"/>
-      <c r="C169" s="14"/>
-      <c r="D169" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E169" s="12"/>
+      <c r="B169" s="14"/>
+      <c r="C169" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D169" s="12"/>
+      <c r="E169" s="10"/>
       <c r="F169" s="10"/>
       <c r="G169" s="10"/>
       <c r="H169" s="10"/>
@@ -15634,17 +15461,16 @@
       <c r="CC169" s="10"/>
       <c r="CD169" s="10"/>
       <c r="CE169" s="10"/>
-      <c r="CF169" s="10"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="10"/>
-      <c r="B170" s="10"/>
-      <c r="C170" s="14"/>
-      <c r="D170" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E170" s="12"/>
+      <c r="B170" s="14"/>
+      <c r="C170" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D170" s="12"/>
+      <c r="E170" s="10"/>
       <c r="F170" s="10"/>
       <c r="G170" s="10"/>
       <c r="H170" s="10"/>
@@ -15723,17 +15549,16 @@
       <c r="CC170" s="10"/>
       <c r="CD170" s="10"/>
       <c r="CE170" s="10"/>
-      <c r="CF170" s="10"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="10"/>
-      <c r="B171" s="10"/>
-      <c r="C171" s="14"/>
-      <c r="D171" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E171" s="12"/>
+      <c r="B171" s="14"/>
+      <c r="C171" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D171" s="12"/>
+      <c r="E171" s="10"/>
       <c r="F171" s="10"/>
       <c r="G171" s="10"/>
       <c r="H171" s="10"/>
@@ -15812,17 +15637,16 @@
       <c r="CC171" s="10"/>
       <c r="CD171" s="10"/>
       <c r="CE171" s="10"/>
-      <c r="CF171" s="10"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="10"/>
-      <c r="B172" s="10"/>
-      <c r="C172" s="14"/>
-      <c r="D172" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E172" s="12"/>
+      <c r="B172" s="14"/>
+      <c r="C172" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D172" s="12"/>
+      <c r="E172" s="10"/>
       <c r="F172" s="10"/>
       <c r="G172" s="10"/>
       <c r="H172" s="10"/>
@@ -15901,17 +15725,16 @@
       <c r="CC172" s="10"/>
       <c r="CD172" s="10"/>
       <c r="CE172" s="10"/>
-      <c r="CF172" s="10"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="10"/>
-      <c r="B173" s="10"/>
-      <c r="C173" s="14"/>
-      <c r="D173" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E173" s="12"/>
+      <c r="B173" s="14"/>
+      <c r="C173" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D173" s="12"/>
+      <c r="E173" s="10"/>
       <c r="F173" s="10"/>
       <c r="G173" s="10"/>
       <c r="H173" s="10"/>
@@ -15990,17 +15813,16 @@
       <c r="CC173" s="10"/>
       <c r="CD173" s="10"/>
       <c r="CE173" s="10"/>
-      <c r="CF173" s="10"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="10"/>
-      <c r="B174" s="10"/>
-      <c r="C174" s="14"/>
-      <c r="D174" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E174" s="12"/>
+      <c r="B174" s="14"/>
+      <c r="C174" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D174" s="12"/>
+      <c r="E174" s="10"/>
       <c r="F174" s="10"/>
       <c r="G174" s="10"/>
       <c r="H174" s="10"/>
@@ -16079,17 +15901,16 @@
       <c r="CC174" s="10"/>
       <c r="CD174" s="10"/>
       <c r="CE174" s="10"/>
-      <c r="CF174" s="10"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="10"/>
-      <c r="B175" s="10"/>
-      <c r="C175" s="14"/>
-      <c r="D175" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E175" s="12"/>
+      <c r="B175" s="14"/>
+      <c r="C175" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D175" s="12"/>
+      <c r="E175" s="10"/>
       <c r="F175" s="10"/>
       <c r="G175" s="10"/>
       <c r="H175" s="10"/>
@@ -16168,17 +15989,16 @@
       <c r="CC175" s="10"/>
       <c r="CD175" s="10"/>
       <c r="CE175" s="10"/>
-      <c r="CF175" s="10"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="10"/>
-      <c r="B176" s="10"/>
-      <c r="C176" s="14"/>
-      <c r="D176" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E176" s="12"/>
+      <c r="B176" s="14"/>
+      <c r="C176" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D176" s="12"/>
+      <c r="E176" s="10"/>
       <c r="F176" s="10"/>
       <c r="G176" s="10"/>
       <c r="H176" s="10"/>
@@ -16257,17 +16077,16 @@
       <c r="CC176" s="10"/>
       <c r="CD176" s="10"/>
       <c r="CE176" s="10"/>
-      <c r="CF176" s="10"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="10"/>
-      <c r="B177" s="10"/>
-      <c r="C177" s="14"/>
-      <c r="D177" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E177" s="12"/>
+      <c r="B177" s="14"/>
+      <c r="C177" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D177" s="12"/>
+      <c r="E177" s="10"/>
       <c r="F177" s="10"/>
       <c r="G177" s="10"/>
       <c r="H177" s="10"/>
@@ -16346,17 +16165,16 @@
       <c r="CC177" s="10"/>
       <c r="CD177" s="10"/>
       <c r="CE177" s="10"/>
-      <c r="CF177" s="10"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="10"/>
-      <c r="B178" s="10"/>
-      <c r="C178" s="14"/>
-      <c r="D178" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E178" s="12"/>
+      <c r="B178" s="14"/>
+      <c r="C178" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D178" s="12"/>
+      <c r="E178" s="10"/>
       <c r="F178" s="10"/>
       <c r="G178" s="10"/>
       <c r="H178" s="10"/>
@@ -16435,17 +16253,16 @@
       <c r="CC178" s="10"/>
       <c r="CD178" s="10"/>
       <c r="CE178" s="10"/>
-      <c r="CF178" s="10"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="10"/>
-      <c r="B179" s="10"/>
-      <c r="C179" s="14"/>
-      <c r="D179" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E179" s="12"/>
+      <c r="B179" s="14"/>
+      <c r="C179" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D179" s="12"/>
+      <c r="E179" s="10"/>
       <c r="F179" s="10"/>
       <c r="G179" s="10"/>
       <c r="H179" s="10"/>
@@ -16524,17 +16341,16 @@
       <c r="CC179" s="10"/>
       <c r="CD179" s="10"/>
       <c r="CE179" s="10"/>
-      <c r="CF179" s="10"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="10"/>
-      <c r="B180" s="10"/>
-      <c r="C180" s="14"/>
-      <c r="D180" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E180" s="12"/>
+      <c r="B180" s="14"/>
+      <c r="C180" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D180" s="12"/>
+      <c r="E180" s="10"/>
       <c r="F180" s="10"/>
       <c r="G180" s="10"/>
       <c r="H180" s="10"/>
@@ -16613,17 +16429,16 @@
       <c r="CC180" s="10"/>
       <c r="CD180" s="10"/>
       <c r="CE180" s="10"/>
-      <c r="CF180" s="10"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="10"/>
-      <c r="B181" s="10"/>
-      <c r="C181" s="14"/>
-      <c r="D181" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E181" s="12"/>
+      <c r="B181" s="14"/>
+      <c r="C181" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D181" s="12"/>
+      <c r="E181" s="10"/>
       <c r="F181" s="10"/>
       <c r="G181" s="10"/>
       <c r="H181" s="10"/>
@@ -16702,17 +16517,16 @@
       <c r="CC181" s="10"/>
       <c r="CD181" s="10"/>
       <c r="CE181" s="10"/>
-      <c r="CF181" s="10"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="10"/>
-      <c r="B182" s="10"/>
-      <c r="C182" s="14"/>
-      <c r="D182" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E182" s="12"/>
+      <c r="B182" s="14"/>
+      <c r="C182" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D182" s="12"/>
+      <c r="E182" s="10"/>
       <c r="F182" s="10"/>
       <c r="G182" s="10"/>
       <c r="H182" s="10"/>
@@ -16791,17 +16605,16 @@
       <c r="CC182" s="10"/>
       <c r="CD182" s="10"/>
       <c r="CE182" s="10"/>
-      <c r="CF182" s="10"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="10"/>
-      <c r="B183" s="10"/>
-      <c r="C183" s="14"/>
-      <c r="D183" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E183" s="12"/>
+      <c r="B183" s="14"/>
+      <c r="C183" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D183" s="12"/>
+      <c r="E183" s="10"/>
       <c r="F183" s="10"/>
       <c r="G183" s="10"/>
       <c r="H183" s="10"/>
@@ -16880,17 +16693,16 @@
       <c r="CC183" s="10"/>
       <c r="CD183" s="10"/>
       <c r="CE183" s="10"/>
-      <c r="CF183" s="10"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="10"/>
-      <c r="B184" s="10"/>
-      <c r="C184" s="14"/>
-      <c r="D184" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E184" s="12"/>
+      <c r="B184" s="14"/>
+      <c r="C184" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D184" s="12"/>
+      <c r="E184" s="10"/>
       <c r="F184" s="10"/>
       <c r="G184" s="10"/>
       <c r="H184" s="10"/>
@@ -16969,17 +16781,16 @@
       <c r="CC184" s="10"/>
       <c r="CD184" s="10"/>
       <c r="CE184" s="10"/>
-      <c r="CF184" s="10"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="10"/>
-      <c r="B185" s="10"/>
-      <c r="C185" s="14"/>
-      <c r="D185" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E185" s="12"/>
+      <c r="B185" s="14"/>
+      <c r="C185" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D185" s="12"/>
+      <c r="E185" s="10"/>
       <c r="F185" s="10"/>
       <c r="G185" s="10"/>
       <c r="H185" s="10"/>
@@ -17058,17 +16869,16 @@
       <c r="CC185" s="10"/>
       <c r="CD185" s="10"/>
       <c r="CE185" s="10"/>
-      <c r="CF185" s="10"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="10"/>
-      <c r="B186" s="10"/>
-      <c r="C186" s="14"/>
-      <c r="D186" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E186" s="12"/>
+      <c r="B186" s="14"/>
+      <c r="C186" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D186" s="12"/>
+      <c r="E186" s="10"/>
       <c r="F186" s="10"/>
       <c r="G186" s="10"/>
       <c r="H186" s="10"/>
@@ -17147,17 +16957,16 @@
       <c r="CC186" s="10"/>
       <c r="CD186" s="10"/>
       <c r="CE186" s="10"/>
-      <c r="CF186" s="10"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="10"/>
-      <c r="B187" s="10"/>
-      <c r="C187" s="14"/>
-      <c r="D187" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E187" s="12"/>
+      <c r="B187" s="14"/>
+      <c r="C187" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D187" s="12"/>
+      <c r="E187" s="10"/>
       <c r="F187" s="10"/>
       <c r="G187" s="10"/>
       <c r="H187" s="10"/>
@@ -17236,17 +17045,16 @@
       <c r="CC187" s="10"/>
       <c r="CD187" s="10"/>
       <c r="CE187" s="10"/>
-      <c r="CF187" s="10"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="10"/>
-      <c r="B188" s="10"/>
-      <c r="C188" s="14"/>
-      <c r="D188" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E188" s="12"/>
+      <c r="B188" s="14"/>
+      <c r="C188" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D188" s="12"/>
+      <c r="E188" s="10"/>
       <c r="F188" s="10"/>
       <c r="G188" s="10"/>
       <c r="H188" s="10"/>
@@ -17325,17 +17133,16 @@
       <c r="CC188" s="10"/>
       <c r="CD188" s="10"/>
       <c r="CE188" s="10"/>
-      <c r="CF188" s="10"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="10"/>
-      <c r="B189" s="10"/>
-      <c r="C189" s="14"/>
-      <c r="D189" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E189" s="12"/>
+      <c r="B189" s="14"/>
+      <c r="C189" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D189" s="12"/>
+      <c r="E189" s="10"/>
       <c r="F189" s="10"/>
       <c r="G189" s="10"/>
       <c r="H189" s="10"/>
@@ -17414,17 +17221,16 @@
       <c r="CC189" s="10"/>
       <c r="CD189" s="10"/>
       <c r="CE189" s="10"/>
-      <c r="CF189" s="10"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="10"/>
-      <c r="B190" s="10"/>
-      <c r="C190" s="14"/>
-      <c r="D190" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E190" s="12"/>
+      <c r="B190" s="14"/>
+      <c r="C190" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D190" s="12"/>
+      <c r="E190" s="10"/>
       <c r="F190" s="10"/>
       <c r="G190" s="10"/>
       <c r="H190" s="10"/>
@@ -17503,17 +17309,16 @@
       <c r="CC190" s="10"/>
       <c r="CD190" s="10"/>
       <c r="CE190" s="10"/>
-      <c r="CF190" s="10"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="10"/>
-      <c r="B191" s="10"/>
-      <c r="C191" s="14"/>
-      <c r="D191" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E191" s="12"/>
+      <c r="B191" s="14"/>
+      <c r="C191" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D191" s="12"/>
+      <c r="E191" s="10"/>
       <c r="F191" s="10"/>
       <c r="G191" s="10"/>
       <c r="H191" s="10"/>
@@ -17592,17 +17397,16 @@
       <c r="CC191" s="10"/>
       <c r="CD191" s="10"/>
       <c r="CE191" s="10"/>
-      <c r="CF191" s="10"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="10"/>
-      <c r="B192" s="10"/>
-      <c r="C192" s="14"/>
-      <c r="D192" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E192" s="12"/>
+      <c r="B192" s="14"/>
+      <c r="C192" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D192" s="12"/>
+      <c r="E192" s="10"/>
       <c r="F192" s="10"/>
       <c r="G192" s="10"/>
       <c r="H192" s="10"/>
@@ -17681,17 +17485,16 @@
       <c r="CC192" s="10"/>
       <c r="CD192" s="10"/>
       <c r="CE192" s="10"/>
-      <c r="CF192" s="10"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="10"/>
-      <c r="B193" s="10"/>
-      <c r="C193" s="14"/>
-      <c r="D193" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E193" s="12"/>
+      <c r="B193" s="14"/>
+      <c r="C193" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D193" s="12"/>
+      <c r="E193" s="10"/>
       <c r="F193" s="10"/>
       <c r="G193" s="10"/>
       <c r="H193" s="10"/>
@@ -17770,17 +17573,16 @@
       <c r="CC193" s="10"/>
       <c r="CD193" s="10"/>
       <c r="CE193" s="10"/>
-      <c r="CF193" s="10"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="10"/>
-      <c r="B194" s="10"/>
-      <c r="C194" s="14"/>
-      <c r="D194" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E194" s="12"/>
+      <c r="B194" s="14"/>
+      <c r="C194" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D194" s="12"/>
+      <c r="E194" s="10"/>
       <c r="F194" s="10"/>
       <c r="G194" s="10"/>
       <c r="H194" s="10"/>
@@ -17859,17 +17661,16 @@
       <c r="CC194" s="10"/>
       <c r="CD194" s="10"/>
       <c r="CE194" s="10"/>
-      <c r="CF194" s="10"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="10"/>
-      <c r="B195" s="10"/>
-      <c r="C195" s="14"/>
-      <c r="D195" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E195" s="12"/>
+      <c r="B195" s="14"/>
+      <c r="C195" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D195" s="12"/>
+      <c r="E195" s="10"/>
       <c r="F195" s="10"/>
       <c r="G195" s="10"/>
       <c r="H195" s="10"/>
@@ -17948,17 +17749,16 @@
       <c r="CC195" s="10"/>
       <c r="CD195" s="10"/>
       <c r="CE195" s="10"/>
-      <c r="CF195" s="10"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="10"/>
-      <c r="B196" s="10"/>
-      <c r="C196" s="14"/>
-      <c r="D196" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E196" s="12"/>
+      <c r="B196" s="14"/>
+      <c r="C196" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D196" s="12"/>
+      <c r="E196" s="10"/>
       <c r="F196" s="10"/>
       <c r="G196" s="10"/>
       <c r="H196" s="10"/>
@@ -18037,17 +17837,16 @@
       <c r="CC196" s="10"/>
       <c r="CD196" s="10"/>
       <c r="CE196" s="10"/>
-      <c r="CF196" s="10"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="10"/>
-      <c r="B197" s="10"/>
-      <c r="C197" s="14"/>
-      <c r="D197" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E197" s="12"/>
+      <c r="B197" s="14"/>
+      <c r="C197" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D197" s="12"/>
+      <c r="E197" s="10"/>
       <c r="F197" s="10"/>
       <c r="G197" s="10"/>
       <c r="H197" s="10"/>
@@ -18126,17 +17925,16 @@
       <c r="CC197" s="10"/>
       <c r="CD197" s="10"/>
       <c r="CE197" s="10"/>
-      <c r="CF197" s="10"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="10"/>
-      <c r="B198" s="10"/>
-      <c r="C198" s="14"/>
-      <c r="D198" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E198" s="12"/>
+      <c r="B198" s="14"/>
+      <c r="C198" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D198" s="12"/>
+      <c r="E198" s="10"/>
       <c r="F198" s="10"/>
       <c r="G198" s="10"/>
       <c r="H198" s="10"/>
@@ -18215,17 +18013,16 @@
       <c r="CC198" s="10"/>
       <c r="CD198" s="10"/>
       <c r="CE198" s="10"/>
-      <c r="CF198" s="10"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="10"/>
-      <c r="B199" s="10"/>
-      <c r="C199" s="14"/>
-      <c r="D199" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E199" s="12"/>
+      <c r="B199" s="14"/>
+      <c r="C199" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D199" s="12"/>
+      <c r="E199" s="10"/>
       <c r="F199" s="10"/>
       <c r="G199" s="10"/>
       <c r="H199" s="10"/>
@@ -18304,17 +18101,16 @@
       <c r="CC199" s="10"/>
       <c r="CD199" s="10"/>
       <c r="CE199" s="10"/>
-      <c r="CF199" s="10"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="10"/>
-      <c r="B200" s="10"/>
-      <c r="C200" s="14"/>
-      <c r="D200" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E200" s="12"/>
+      <c r="B200" s="14"/>
+      <c r="C200" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D200" s="12"/>
+      <c r="E200" s="10"/>
       <c r="F200" s="10"/>
       <c r="G200" s="10"/>
       <c r="H200" s="10"/>
@@ -18393,17 +18189,16 @@
       <c r="CC200" s="10"/>
       <c r="CD200" s="10"/>
       <c r="CE200" s="10"/>
-      <c r="CF200" s="10"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="10"/>
-      <c r="B201" s="10"/>
-      <c r="C201" s="14"/>
-      <c r="D201" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E201" s="12"/>
+      <c r="B201" s="14"/>
+      <c r="C201" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D201" s="12"/>
+      <c r="E201" s="10"/>
       <c r="F201" s="10"/>
       <c r="G201" s="10"/>
       <c r="H201" s="10"/>
@@ -18482,17 +18277,16 @@
       <c r="CC201" s="10"/>
       <c r="CD201" s="10"/>
       <c r="CE201" s="10"/>
-      <c r="CF201" s="10"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="10"/>
-      <c r="B202" s="10"/>
-      <c r="C202" s="14"/>
-      <c r="D202" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E202" s="12"/>
+      <c r="B202" s="14"/>
+      <c r="C202" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D202" s="12"/>
+      <c r="E202" s="10"/>
       <c r="F202" s="10"/>
       <c r="G202" s="10"/>
       <c r="H202" s="10"/>
@@ -18571,17 +18365,16 @@
       <c r="CC202" s="10"/>
       <c r="CD202" s="10"/>
       <c r="CE202" s="10"/>
-      <c r="CF202" s="10"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="10"/>
-      <c r="B203" s="10"/>
-      <c r="C203" s="14"/>
-      <c r="D203" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E203" s="12"/>
+      <c r="B203" s="14"/>
+      <c r="C203" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D203" s="12"/>
+      <c r="E203" s="10"/>
       <c r="F203" s="10"/>
       <c r="G203" s="10"/>
       <c r="H203" s="10"/>
@@ -18660,17 +18453,16 @@
       <c r="CC203" s="10"/>
       <c r="CD203" s="10"/>
       <c r="CE203" s="10"/>
-      <c r="CF203" s="10"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="10"/>
-      <c r="B204" s="10"/>
-      <c r="C204" s="14"/>
-      <c r="D204" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E204" s="12"/>
+      <c r="B204" s="14"/>
+      <c r="C204" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D204" s="12"/>
+      <c r="E204" s="10"/>
       <c r="F204" s="10"/>
       <c r="G204" s="10"/>
       <c r="H204" s="10"/>
@@ -18749,17 +18541,16 @@
       <c r="CC204" s="10"/>
       <c r="CD204" s="10"/>
       <c r="CE204" s="10"/>
-      <c r="CF204" s="10"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="10"/>
-      <c r="B205" s="10"/>
-      <c r="C205" s="14"/>
-      <c r="D205" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E205" s="12"/>
+      <c r="B205" s="14"/>
+      <c r="C205" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D205" s="12"/>
+      <c r="E205" s="10"/>
       <c r="F205" s="10"/>
       <c r="G205" s="10"/>
       <c r="H205" s="10"/>
@@ -18838,17 +18629,16 @@
       <c r="CC205" s="10"/>
       <c r="CD205" s="10"/>
       <c r="CE205" s="10"/>
-      <c r="CF205" s="10"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="10"/>
-      <c r="B206" s="10"/>
-      <c r="C206" s="14"/>
-      <c r="D206" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E206" s="12"/>
+      <c r="B206" s="14"/>
+      <c r="C206" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D206" s="12"/>
+      <c r="E206" s="10"/>
       <c r="F206" s="10"/>
       <c r="G206" s="10"/>
       <c r="H206" s="10"/>
@@ -18927,17 +18717,16 @@
       <c r="CC206" s="10"/>
       <c r="CD206" s="10"/>
       <c r="CE206" s="10"/>
-      <c r="CF206" s="10"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="10"/>
-      <c r="B207" s="10"/>
-      <c r="C207" s="14"/>
-      <c r="D207" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E207" s="12"/>
+      <c r="B207" s="14"/>
+      <c r="C207" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D207" s="12"/>
+      <c r="E207" s="10"/>
       <c r="F207" s="10"/>
       <c r="G207" s="10"/>
       <c r="H207" s="10"/>
@@ -19016,17 +18805,16 @@
       <c r="CC207" s="10"/>
       <c r="CD207" s="10"/>
       <c r="CE207" s="10"/>
-      <c r="CF207" s="10"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="10"/>
-      <c r="B208" s="10"/>
-      <c r="C208" s="14"/>
-      <c r="D208" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E208" s="12"/>
+      <c r="B208" s="14"/>
+      <c r="C208" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D208" s="12"/>
+      <c r="E208" s="10"/>
       <c r="F208" s="10"/>
       <c r="G208" s="10"/>
       <c r="H208" s="10"/>
@@ -19105,17 +18893,16 @@
       <c r="CC208" s="10"/>
       <c r="CD208" s="10"/>
       <c r="CE208" s="10"/>
-      <c r="CF208" s="10"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="10"/>
-      <c r="B209" s="10"/>
-      <c r="C209" s="14"/>
-      <c r="D209" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E209" s="12"/>
+      <c r="B209" s="14"/>
+      <c r="C209" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D209" s="12"/>
+      <c r="E209" s="10"/>
       <c r="F209" s="10"/>
       <c r="G209" s="10"/>
       <c r="H209" s="10"/>
@@ -19194,17 +18981,16 @@
       <c r="CC209" s="10"/>
       <c r="CD209" s="10"/>
       <c r="CE209" s="10"/>
-      <c r="CF209" s="10"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="10"/>
-      <c r="B210" s="10"/>
-      <c r="C210" s="14"/>
-      <c r="D210" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E210" s="12"/>
+      <c r="B210" s="14"/>
+      <c r="C210" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D210" s="12"/>
+      <c r="E210" s="10"/>
       <c r="F210" s="10"/>
       <c r="G210" s="10"/>
       <c r="H210" s="10"/>
@@ -19283,17 +19069,16 @@
       <c r="CC210" s="10"/>
       <c r="CD210" s="10"/>
       <c r="CE210" s="10"/>
-      <c r="CF210" s="10"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="10"/>
-      <c r="B211" s="10"/>
-      <c r="C211" s="14"/>
-      <c r="D211" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E211" s="12"/>
+      <c r="B211" s="14"/>
+      <c r="C211" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D211" s="12"/>
+      <c r="E211" s="10"/>
       <c r="F211" s="10"/>
       <c r="G211" s="10"/>
       <c r="H211" s="10"/>
@@ -19372,17 +19157,16 @@
       <c r="CC211" s="10"/>
       <c r="CD211" s="10"/>
       <c r="CE211" s="10"/>
-      <c r="CF211" s="10"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="10"/>
-      <c r="B212" s="10"/>
-      <c r="C212" s="14"/>
-      <c r="D212" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E212" s="12"/>
+      <c r="B212" s="14"/>
+      <c r="C212" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D212" s="12"/>
+      <c r="E212" s="10"/>
       <c r="F212" s="10"/>
       <c r="G212" s="10"/>
       <c r="H212" s="10"/>
@@ -19461,17 +19245,16 @@
       <c r="CC212" s="10"/>
       <c r="CD212" s="10"/>
       <c r="CE212" s="10"/>
-      <c r="CF212" s="10"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="10"/>
-      <c r="B213" s="10"/>
-      <c r="C213" s="14"/>
-      <c r="D213" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E213" s="12"/>
+      <c r="B213" s="14"/>
+      <c r="C213" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D213" s="12"/>
+      <c r="E213" s="10"/>
       <c r="F213" s="10"/>
       <c r="G213" s="10"/>
       <c r="H213" s="10"/>
@@ -19550,17 +19333,16 @@
       <c r="CC213" s="10"/>
       <c r="CD213" s="10"/>
       <c r="CE213" s="10"/>
-      <c r="CF213" s="10"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="10"/>
-      <c r="B214" s="10"/>
-      <c r="C214" s="14"/>
-      <c r="D214" s="11" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("C"&amp;ROW())),"",INDIRECT("C"&amp;ROW())-SUM(INDIRECT("F"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
-        <v/>
-      </c>
-      <c r="E214" s="12"/>
+      <c r="B214" s="14"/>
+      <c r="C214" s="11" t="str">
+        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+      <c r="D214" s="12"/>
+      <c r="E214" s="10"/>
       <c r="F214" s="10"/>
       <c r="G214" s="10"/>
       <c r="H214" s="10"/>
@@ -19639,10 +19421,9 @@
       <c r="CC214" s="10"/>
       <c r="CD214" s="10"/>
       <c r="CE214" s="10"/>
-      <c r="CF214" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C1048576 D1:D1048576">
+  <conditionalFormatting sqref="B2:B1048576 C1:C1048576">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/src/fnschool/canteen/data/consuming.xlsx
+++ b/src/fnschool/canteen/data/consuming.xlsx
@@ -224,17 +224,18 @@
   <dxfs count="1">
     <dxf>
       <font>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <color rgb="FF006600"/>
-        <sz val="12"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFCCFFCC"/>
+          <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -247,8 +248,8 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF006600"/>
+      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -19423,7 +19424,7 @@
       <c r="CE214" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B1048576 C1:C1048576">
+  <conditionalFormatting sqref="C2:C1024">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/src/fnschool/canteen/data/consuming.xlsx
+++ b/src/fnschool/canteen/data/consuming.xlsx
@@ -38,13 +38,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
     <numFmt numFmtId="167" formatCode="@"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00000000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="170" formatCode="#,##0.00000000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -199,11 +200,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/src/fnschool/canteen/data/consuming.xlsx
+++ b/src/fnschool/canteen/data/consuming.xlsx
@@ -19453,8 +19453,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/src/fnschool/canteen/data/consuming.xlsx
+++ b/src/fnschool/canteen/data/consuming.xlsx
@@ -281,7 +281,6 @@
           <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -296,7 +295,6 @@
           <bgColor rgb="FF808080"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -310,7 +308,6 @@
           <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -487,7 +484,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CF214"/>
+  <dimension ref="A1:CF256"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.91"/>
@@ -847,7 +844,7 @@
       <c r="A3" s="15"/>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D3" s="18"/>
@@ -935,7 +932,7 @@
       <c r="A4" s="15"/>
       <c r="B4" s="16"/>
       <c r="C4" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D4" s="18"/>
@@ -1023,7 +1020,7 @@
       <c r="A5" s="15"/>
       <c r="B5" s="16"/>
       <c r="C5" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D5" s="21"/>
@@ -1111,7 +1108,7 @@
       <c r="A6" s="15"/>
       <c r="B6" s="16"/>
       <c r="C6" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D6" s="18"/>
@@ -1199,7 +1196,7 @@
       <c r="A7" s="15"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D7" s="18"/>
@@ -1287,7 +1284,7 @@
       <c r="A8" s="15"/>
       <c r="B8" s="16"/>
       <c r="C8" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D8" s="18"/>
@@ -1375,7 +1372,7 @@
       <c r="A9" s="15"/>
       <c r="B9" s="16"/>
       <c r="C9" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D9" s="18"/>
@@ -1463,7 +1460,7 @@
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D10" s="18"/>
@@ -1551,7 +1548,7 @@
       <c r="A11" s="15"/>
       <c r="B11" s="16"/>
       <c r="C11" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D11" s="18"/>
@@ -1639,7 +1636,7 @@
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D12" s="18"/>
@@ -1727,7 +1724,7 @@
       <c r="A13" s="15"/>
       <c r="B13" s="16"/>
       <c r="C13" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D13" s="18"/>
@@ -1815,7 +1812,7 @@
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D14" s="18"/>
@@ -1903,7 +1900,7 @@
       <c r="A15" s="15"/>
       <c r="B15" s="16"/>
       <c r="C15" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D15" s="18"/>
@@ -1991,7 +1988,7 @@
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D16" s="21"/>
@@ -2079,7 +2076,7 @@
       <c r="A17" s="15"/>
       <c r="B17" s="16"/>
       <c r="C17" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D17" s="21"/>
@@ -2167,7 +2164,7 @@
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D18" s="18"/>
@@ -2255,7 +2252,7 @@
       <c r="A19" s="15"/>
       <c r="B19" s="16"/>
       <c r="C19" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D19" s="21"/>
@@ -2343,7 +2340,7 @@
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D20" s="18"/>
@@ -2431,7 +2428,7 @@
       <c r="A21" s="15"/>
       <c r="B21" s="16"/>
       <c r="C21" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D21" s="18"/>
@@ -2519,7 +2516,7 @@
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D22" s="18"/>
@@ -2607,7 +2604,7 @@
       <c r="A23" s="15"/>
       <c r="B23" s="16"/>
       <c r="C23" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D23" s="21"/>
@@ -2695,7 +2692,7 @@
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D24" s="18"/>
@@ -2783,7 +2780,7 @@
       <c r="A25" s="15"/>
       <c r="B25" s="16"/>
       <c r="C25" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D25" s="18"/>
@@ -2871,7 +2868,7 @@
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D26" s="18"/>
@@ -2959,7 +2956,7 @@
       <c r="A27" s="15"/>
       <c r="B27" s="22"/>
       <c r="C27" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D27" s="18"/>
@@ -3047,7 +3044,7 @@
       <c r="A28" s="15"/>
       <c r="B28" s="22"/>
       <c r="C28" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D28" s="18"/>
@@ -3135,7 +3132,7 @@
       <c r="A29" s="15"/>
       <c r="B29" s="22"/>
       <c r="C29" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D29" s="18"/>
@@ -3223,7 +3220,7 @@
       <c r="A30" s="15"/>
       <c r="B30" s="22"/>
       <c r="C30" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D30" s="18"/>
@@ -3311,7 +3308,7 @@
       <c r="A31" s="15"/>
       <c r="B31" s="22"/>
       <c r="C31" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D31" s="18"/>
@@ -3399,7 +3396,7 @@
       <c r="A32" s="15"/>
       <c r="B32" s="22"/>
       <c r="C32" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D32" s="18"/>
@@ -3487,7 +3484,7 @@
       <c r="A33" s="15"/>
       <c r="B33" s="22"/>
       <c r="C33" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D33" s="18"/>
@@ -3575,7 +3572,7 @@
       <c r="A34" s="15"/>
       <c r="B34" s="22"/>
       <c r="C34" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D34" s="18"/>
@@ -3663,7 +3660,7 @@
       <c r="A35" s="15"/>
       <c r="B35" s="22"/>
       <c r="C35" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D35" s="18"/>
@@ -3751,7 +3748,7 @@
       <c r="A36" s="15"/>
       <c r="B36" s="22"/>
       <c r="C36" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D36" s="18"/>
@@ -3839,7 +3836,7 @@
       <c r="A37" s="15"/>
       <c r="B37" s="22"/>
       <c r="C37" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D37" s="18"/>
@@ -3927,7 +3924,7 @@
       <c r="A38" s="15"/>
       <c r="B38" s="22"/>
       <c r="C38" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D38" s="18"/>
@@ -4015,7 +4012,7 @@
       <c r="A39" s="15"/>
       <c r="B39" s="22"/>
       <c r="C39" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D39" s="18"/>
@@ -4103,7 +4100,7 @@
       <c r="A40" s="15"/>
       <c r="B40" s="22"/>
       <c r="C40" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D40" s="18"/>
@@ -4191,7 +4188,7 @@
       <c r="A41" s="15"/>
       <c r="B41" s="22"/>
       <c r="C41" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D41" s="18"/>
@@ -4279,7 +4276,7 @@
       <c r="A42" s="15"/>
       <c r="B42" s="22"/>
       <c r="C42" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D42" s="18"/>
@@ -4367,7 +4364,7 @@
       <c r="A43" s="15"/>
       <c r="B43" s="22"/>
       <c r="C43" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D43" s="18"/>
@@ -4455,7 +4452,7 @@
       <c r="A44" s="15"/>
       <c r="B44" s="22"/>
       <c r="C44" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D44" s="18"/>
@@ -4543,7 +4540,7 @@
       <c r="A45" s="15"/>
       <c r="B45" s="22"/>
       <c r="C45" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D45" s="18"/>
@@ -4631,7 +4628,7 @@
       <c r="A46" s="15"/>
       <c r="B46" s="22"/>
       <c r="C46" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D46" s="18"/>
@@ -4719,7 +4716,7 @@
       <c r="A47" s="15"/>
       <c r="B47" s="22"/>
       <c r="C47" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D47" s="18"/>
@@ -4807,7 +4804,7 @@
       <c r="A48" s="15"/>
       <c r="B48" s="22"/>
       <c r="C48" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D48" s="18"/>
@@ -4895,7 +4892,7 @@
       <c r="A49" s="15"/>
       <c r="B49" s="22"/>
       <c r="C49" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D49" s="18"/>
@@ -4983,7 +4980,7 @@
       <c r="A50" s="15"/>
       <c r="B50" s="22"/>
       <c r="C50" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D50" s="18"/>
@@ -5071,7 +5068,7 @@
       <c r="A51" s="15"/>
       <c r="B51" s="22"/>
       <c r="C51" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D51" s="18"/>
@@ -5159,7 +5156,7 @@
       <c r="A52" s="15"/>
       <c r="B52" s="22"/>
       <c r="C52" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D52" s="18"/>
@@ -5247,7 +5244,7 @@
       <c r="A53" s="15"/>
       <c r="B53" s="22"/>
       <c r="C53" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D53" s="18"/>
@@ -5335,7 +5332,7 @@
       <c r="A54" s="15"/>
       <c r="B54" s="22"/>
       <c r="C54" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D54" s="18"/>
@@ -5423,7 +5420,7 @@
       <c r="A55" s="15"/>
       <c r="B55" s="22"/>
       <c r="C55" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D55" s="18"/>
@@ -5511,7 +5508,7 @@
       <c r="A56" s="15"/>
       <c r="B56" s="22"/>
       <c r="C56" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D56" s="18"/>
@@ -5599,7 +5596,7 @@
       <c r="A57" s="15"/>
       <c r="B57" s="22"/>
       <c r="C57" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D57" s="18"/>
@@ -5687,7 +5684,7 @@
       <c r="A58" s="15"/>
       <c r="B58" s="22"/>
       <c r="C58" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D58" s="18"/>
@@ -5775,7 +5772,7 @@
       <c r="A59" s="15"/>
       <c r="B59" s="22"/>
       <c r="C59" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D59" s="18"/>
@@ -5863,7 +5860,7 @@
       <c r="A60" s="15"/>
       <c r="B60" s="22"/>
       <c r="C60" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D60" s="18"/>
@@ -5951,7 +5948,7 @@
       <c r="A61" s="15"/>
       <c r="B61" s="22"/>
       <c r="C61" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D61" s="18"/>
@@ -6039,7 +6036,7 @@
       <c r="A62" s="15"/>
       <c r="B62" s="22"/>
       <c r="C62" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D62" s="18"/>
@@ -6127,7 +6124,7 @@
       <c r="A63" s="15"/>
       <c r="B63" s="22"/>
       <c r="C63" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D63" s="18"/>
@@ -6215,7 +6212,7 @@
       <c r="A64" s="15"/>
       <c r="B64" s="22"/>
       <c r="C64" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D64" s="18"/>
@@ -6303,7 +6300,7 @@
       <c r="A65" s="15"/>
       <c r="B65" s="22"/>
       <c r="C65" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D65" s="18"/>
@@ -6391,7 +6388,7 @@
       <c r="A66" s="15"/>
       <c r="B66" s="22"/>
       <c r="C66" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D66" s="18"/>
@@ -6479,7 +6476,7 @@
       <c r="A67" s="15"/>
       <c r="B67" s="22"/>
       <c r="C67" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D67" s="18"/>
@@ -6567,7 +6564,7 @@
       <c r="A68" s="15"/>
       <c r="B68" s="22"/>
       <c r="C68" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D68" s="18"/>
@@ -6655,7 +6652,7 @@
       <c r="A69" s="15"/>
       <c r="B69" s="22"/>
       <c r="C69" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D69" s="18"/>
@@ -6743,7 +6740,7 @@
       <c r="A70" s="15"/>
       <c r="B70" s="22"/>
       <c r="C70" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D70" s="18"/>
@@ -6831,7 +6828,7 @@
       <c r="A71" s="15"/>
       <c r="B71" s="22"/>
       <c r="C71" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D71" s="18"/>
@@ -6919,7 +6916,7 @@
       <c r="A72" s="15"/>
       <c r="B72" s="22"/>
       <c r="C72" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D72" s="18"/>
@@ -7007,7 +7004,7 @@
       <c r="A73" s="15"/>
       <c r="B73" s="22"/>
       <c r="C73" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D73" s="18"/>
@@ -7095,7 +7092,7 @@
       <c r="A74" s="15"/>
       <c r="B74" s="22"/>
       <c r="C74" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D74" s="18"/>
@@ -7183,7 +7180,7 @@
       <c r="A75" s="15"/>
       <c r="B75" s="22"/>
       <c r="C75" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D75" s="18"/>
@@ -7271,7 +7268,7 @@
       <c r="A76" s="15"/>
       <c r="B76" s="22"/>
       <c r="C76" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D76" s="18"/>
@@ -7359,7 +7356,7 @@
       <c r="A77" s="15"/>
       <c r="B77" s="22"/>
       <c r="C77" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D77" s="18"/>
@@ -7447,7 +7444,7 @@
       <c r="A78" s="15"/>
       <c r="B78" s="22"/>
       <c r="C78" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D78" s="18"/>
@@ -7535,7 +7532,7 @@
       <c r="A79" s="15"/>
       <c r="B79" s="22"/>
       <c r="C79" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D79" s="18"/>
@@ -7623,7 +7620,7 @@
       <c r="A80" s="15"/>
       <c r="B80" s="22"/>
       <c r="C80" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D80" s="18"/>
@@ -7711,7 +7708,7 @@
       <c r="A81" s="15"/>
       <c r="B81" s="22"/>
       <c r="C81" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D81" s="18"/>
@@ -7799,7 +7796,7 @@
       <c r="A82" s="15"/>
       <c r="B82" s="22"/>
       <c r="C82" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D82" s="18"/>
@@ -7887,7 +7884,7 @@
       <c r="A83" s="15"/>
       <c r="B83" s="22"/>
       <c r="C83" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D83" s="18"/>
@@ -7975,7 +7972,7 @@
       <c r="A84" s="15"/>
       <c r="B84" s="22"/>
       <c r="C84" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D84" s="18"/>
@@ -8063,7 +8060,7 @@
       <c r="A85" s="15"/>
       <c r="B85" s="22"/>
       <c r="C85" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D85" s="18"/>
@@ -8151,7 +8148,7 @@
       <c r="A86" s="15"/>
       <c r="B86" s="22"/>
       <c r="C86" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D86" s="18"/>
@@ -8239,7 +8236,7 @@
       <c r="A87" s="15"/>
       <c r="B87" s="22"/>
       <c r="C87" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D87" s="18"/>
@@ -8327,7 +8324,7 @@
       <c r="A88" s="15"/>
       <c r="B88" s="22"/>
       <c r="C88" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D88" s="18"/>
@@ -8415,7 +8412,7 @@
       <c r="A89" s="15"/>
       <c r="B89" s="22"/>
       <c r="C89" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D89" s="18"/>
@@ -8503,7 +8500,7 @@
       <c r="A90" s="15"/>
       <c r="B90" s="22"/>
       <c r="C90" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D90" s="18"/>
@@ -8591,7 +8588,7 @@
       <c r="A91" s="15"/>
       <c r="B91" s="22"/>
       <c r="C91" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D91" s="18"/>
@@ -8679,7 +8676,7 @@
       <c r="A92" s="15"/>
       <c r="B92" s="22"/>
       <c r="C92" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D92" s="18"/>
@@ -8767,7 +8764,7 @@
       <c r="A93" s="15"/>
       <c r="B93" s="22"/>
       <c r="C93" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D93" s="18"/>
@@ -8855,7 +8852,7 @@
       <c r="A94" s="15"/>
       <c r="B94" s="22"/>
       <c r="C94" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D94" s="18"/>
@@ -8943,7 +8940,7 @@
       <c r="A95" s="15"/>
       <c r="B95" s="22"/>
       <c r="C95" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D95" s="18"/>
@@ -9031,7 +9028,7 @@
       <c r="A96" s="15"/>
       <c r="B96" s="22"/>
       <c r="C96" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D96" s="18"/>
@@ -9119,7 +9116,7 @@
       <c r="A97" s="15"/>
       <c r="B97" s="22"/>
       <c r="C97" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D97" s="18"/>
@@ -9207,7 +9204,7 @@
       <c r="A98" s="15"/>
       <c r="B98" s="22"/>
       <c r="C98" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D98" s="18"/>
@@ -9295,7 +9292,7 @@
       <c r="A99" s="15"/>
       <c r="B99" s="22"/>
       <c r="C99" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D99" s="18"/>
@@ -9383,7 +9380,7 @@
       <c r="A100" s="15"/>
       <c r="B100" s="22"/>
       <c r="C100" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D100" s="18"/>
@@ -9471,7 +9468,7 @@
       <c r="A101" s="15"/>
       <c r="B101" s="22"/>
       <c r="C101" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D101" s="18"/>
@@ -9559,7 +9556,7 @@
       <c r="A102" s="15"/>
       <c r="B102" s="22"/>
       <c r="C102" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D102" s="18"/>
@@ -9647,7 +9644,7 @@
       <c r="A103" s="15"/>
       <c r="B103" s="22"/>
       <c r="C103" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D103" s="18"/>
@@ -9735,7 +9732,7 @@
       <c r="A104" s="15"/>
       <c r="B104" s="22"/>
       <c r="C104" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D104" s="18"/>
@@ -9823,7 +9820,7 @@
       <c r="A105" s="15"/>
       <c r="B105" s="22"/>
       <c r="C105" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D105" s="18"/>
@@ -9911,7 +9908,7 @@
       <c r="A106" s="15"/>
       <c r="B106" s="22"/>
       <c r="C106" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D106" s="18"/>
@@ -9999,7 +9996,7 @@
       <c r="A107" s="15"/>
       <c r="B107" s="22"/>
       <c r="C107" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D107" s="18"/>
@@ -10087,7 +10084,7 @@
       <c r="A108" s="15"/>
       <c r="B108" s="22"/>
       <c r="C108" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D108" s="18"/>
@@ -10175,7 +10172,7 @@
       <c r="A109" s="15"/>
       <c r="B109" s="22"/>
       <c r="C109" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D109" s="18"/>
@@ -10263,7 +10260,7 @@
       <c r="A110" s="15"/>
       <c r="B110" s="22"/>
       <c r="C110" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D110" s="18"/>
@@ -10351,7 +10348,7 @@
       <c r="A111" s="15"/>
       <c r="B111" s="22"/>
       <c r="C111" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D111" s="18"/>
@@ -10439,7 +10436,7 @@
       <c r="A112" s="15"/>
       <c r="B112" s="22"/>
       <c r="C112" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D112" s="18"/>
@@ -10527,7 +10524,7 @@
       <c r="A113" s="15"/>
       <c r="B113" s="22"/>
       <c r="C113" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D113" s="18"/>
@@ -10615,7 +10612,7 @@
       <c r="A114" s="15"/>
       <c r="B114" s="22"/>
       <c r="C114" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D114" s="18"/>
@@ -10703,7 +10700,7 @@
       <c r="A115" s="15"/>
       <c r="B115" s="22"/>
       <c r="C115" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D115" s="18"/>
@@ -10791,7 +10788,7 @@
       <c r="A116" s="15"/>
       <c r="B116" s="22"/>
       <c r="C116" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D116" s="18"/>
@@ -10879,7 +10876,7 @@
       <c r="A117" s="15"/>
       <c r="B117" s="22"/>
       <c r="C117" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D117" s="18"/>
@@ -10967,7 +10964,7 @@
       <c r="A118" s="15"/>
       <c r="B118" s="22"/>
       <c r="C118" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D118" s="18"/>
@@ -11055,7 +11052,7 @@
       <c r="A119" s="15"/>
       <c r="B119" s="22"/>
       <c r="C119" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D119" s="18"/>
@@ -11143,7 +11140,7 @@
       <c r="A120" s="15"/>
       <c r="B120" s="22"/>
       <c r="C120" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D120" s="18"/>
@@ -11231,7 +11228,7 @@
       <c r="A121" s="15"/>
       <c r="B121" s="22"/>
       <c r="C121" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D121" s="18"/>
@@ -11319,7 +11316,7 @@
       <c r="A122" s="15"/>
       <c r="B122" s="22"/>
       <c r="C122" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D122" s="18"/>
@@ -11407,7 +11404,7 @@
       <c r="A123" s="15"/>
       <c r="B123" s="22"/>
       <c r="C123" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D123" s="18"/>
@@ -11495,7 +11492,7 @@
       <c r="A124" s="15"/>
       <c r="B124" s="22"/>
       <c r="C124" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D124" s="18"/>
@@ -11583,7 +11580,7 @@
       <c r="A125" s="15"/>
       <c r="B125" s="22"/>
       <c r="C125" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D125" s="18"/>
@@ -11671,7 +11668,7 @@
       <c r="A126" s="15"/>
       <c r="B126" s="22"/>
       <c r="C126" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D126" s="18"/>
@@ -11759,7 +11756,7 @@
       <c r="A127" s="15"/>
       <c r="B127" s="22"/>
       <c r="C127" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D127" s="18"/>
@@ -11847,7 +11844,7 @@
       <c r="A128" s="15"/>
       <c r="B128" s="22"/>
       <c r="C128" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D128" s="18"/>
@@ -11935,7 +11932,7 @@
       <c r="A129" s="15"/>
       <c r="B129" s="22"/>
       <c r="C129" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D129" s="18"/>
@@ -12023,7 +12020,7 @@
       <c r="A130" s="15"/>
       <c r="B130" s="22"/>
       <c r="C130" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D130" s="18"/>
@@ -12111,7 +12108,7 @@
       <c r="A131" s="15"/>
       <c r="B131" s="22"/>
       <c r="C131" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D131" s="18"/>
@@ -12199,7 +12196,7 @@
       <c r="A132" s="15"/>
       <c r="B132" s="22"/>
       <c r="C132" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D132" s="18"/>
@@ -12287,7 +12284,7 @@
       <c r="A133" s="15"/>
       <c r="B133" s="22"/>
       <c r="C133" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D133" s="18"/>
@@ -12375,7 +12372,7 @@
       <c r="A134" s="15"/>
       <c r="B134" s="22"/>
       <c r="C134" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D134" s="18"/>
@@ -12463,7 +12460,7 @@
       <c r="A135" s="15"/>
       <c r="B135" s="22"/>
       <c r="C135" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D135" s="18"/>
@@ -12551,7 +12548,7 @@
       <c r="A136" s="15"/>
       <c r="B136" s="22"/>
       <c r="C136" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D136" s="18"/>
@@ -12639,7 +12636,7 @@
       <c r="A137" s="15"/>
       <c r="B137" s="22"/>
       <c r="C137" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D137" s="18"/>
@@ -12727,7 +12724,7 @@
       <c r="A138" s="15"/>
       <c r="B138" s="22"/>
       <c r="C138" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D138" s="18"/>
@@ -12815,7 +12812,7 @@
       <c r="A139" s="15"/>
       <c r="B139" s="22"/>
       <c r="C139" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D139" s="18"/>
@@ -12903,7 +12900,7 @@
       <c r="A140" s="15"/>
       <c r="B140" s="22"/>
       <c r="C140" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D140" s="18"/>
@@ -12991,7 +12988,7 @@
       <c r="A141" s="15"/>
       <c r="B141" s="22"/>
       <c r="C141" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D141" s="18"/>
@@ -13079,7 +13076,7 @@
       <c r="A142" s="15"/>
       <c r="B142" s="22"/>
       <c r="C142" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D142" s="18"/>
@@ -13167,7 +13164,7 @@
       <c r="A143" s="15"/>
       <c r="B143" s="22"/>
       <c r="C143" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D143" s="18"/>
@@ -13255,7 +13252,7 @@
       <c r="A144" s="15"/>
       <c r="B144" s="22"/>
       <c r="C144" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D144" s="18"/>
@@ -13343,7 +13340,7 @@
       <c r="A145" s="15"/>
       <c r="B145" s="22"/>
       <c r="C145" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D145" s="18"/>
@@ -13431,7 +13428,7 @@
       <c r="A146" s="15"/>
       <c r="B146" s="22"/>
       <c r="C146" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D146" s="18"/>
@@ -13519,7 +13516,7 @@
       <c r="A147" s="15"/>
       <c r="B147" s="22"/>
       <c r="C147" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D147" s="18"/>
@@ -13607,7 +13604,7 @@
       <c r="A148" s="15"/>
       <c r="B148" s="22"/>
       <c r="C148" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D148" s="18"/>
@@ -13695,7 +13692,7 @@
       <c r="A149" s="15"/>
       <c r="B149" s="22"/>
       <c r="C149" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D149" s="18"/>
@@ -13783,7 +13780,7 @@
       <c r="A150" s="15"/>
       <c r="B150" s="22"/>
       <c r="C150" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D150" s="18"/>
@@ -13871,7 +13868,7 @@
       <c r="A151" s="15"/>
       <c r="B151" s="22"/>
       <c r="C151" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D151" s="18"/>
@@ -13959,7 +13956,7 @@
       <c r="A152" s="15"/>
       <c r="B152" s="22"/>
       <c r="C152" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D152" s="18"/>
@@ -14047,7 +14044,7 @@
       <c r="A153" s="15"/>
       <c r="B153" s="22"/>
       <c r="C153" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D153" s="18"/>
@@ -14135,7 +14132,7 @@
       <c r="A154" s="15"/>
       <c r="B154" s="22"/>
       <c r="C154" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D154" s="18"/>
@@ -14223,7 +14220,7 @@
       <c r="A155" s="15"/>
       <c r="B155" s="22"/>
       <c r="C155" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D155" s="18"/>
@@ -14311,7 +14308,7 @@
       <c r="A156" s="15"/>
       <c r="B156" s="22"/>
       <c r="C156" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D156" s="18"/>
@@ -14399,7 +14396,7 @@
       <c r="A157" s="15"/>
       <c r="B157" s="22"/>
       <c r="C157" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D157" s="18"/>
@@ -14487,7 +14484,7 @@
       <c r="A158" s="15"/>
       <c r="B158" s="22"/>
       <c r="C158" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D158" s="18"/>
@@ -14575,7 +14572,7 @@
       <c r="A159" s="15"/>
       <c r="B159" s="22"/>
       <c r="C159" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D159" s="18"/>
@@ -14663,7 +14660,7 @@
       <c r="A160" s="15"/>
       <c r="B160" s="22"/>
       <c r="C160" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D160" s="18"/>
@@ -14751,7 +14748,7 @@
       <c r="A161" s="15"/>
       <c r="B161" s="22"/>
       <c r="C161" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D161" s="18"/>
@@ -14839,7 +14836,7 @@
       <c r="A162" s="15"/>
       <c r="B162" s="22"/>
       <c r="C162" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D162" s="18"/>
@@ -14927,7 +14924,7 @@
       <c r="A163" s="15"/>
       <c r="B163" s="22"/>
       <c r="C163" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D163" s="18"/>
@@ -15015,7 +15012,7 @@
       <c r="A164" s="15"/>
       <c r="B164" s="22"/>
       <c r="C164" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D164" s="18"/>
@@ -15103,7 +15100,7 @@
       <c r="A165" s="15"/>
       <c r="B165" s="22"/>
       <c r="C165" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D165" s="18"/>
@@ -15191,7 +15188,7 @@
       <c r="A166" s="15"/>
       <c r="B166" s="22"/>
       <c r="C166" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D166" s="18"/>
@@ -15279,7 +15276,7 @@
       <c r="A167" s="15"/>
       <c r="B167" s="22"/>
       <c r="C167" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D167" s="18"/>
@@ -15367,7 +15364,7 @@
       <c r="A168" s="15"/>
       <c r="B168" s="22"/>
       <c r="C168" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D168" s="18"/>
@@ -15455,7 +15452,7 @@
       <c r="A169" s="15"/>
       <c r="B169" s="22"/>
       <c r="C169" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D169" s="18"/>
@@ -15543,7 +15540,7 @@
       <c r="A170" s="15"/>
       <c r="B170" s="22"/>
       <c r="C170" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D170" s="18"/>
@@ -15631,7 +15628,7 @@
       <c r="A171" s="15"/>
       <c r="B171" s="22"/>
       <c r="C171" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D171" s="18"/>
@@ -15719,7 +15716,7 @@
       <c r="A172" s="15"/>
       <c r="B172" s="22"/>
       <c r="C172" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D172" s="18"/>
@@ -15807,7 +15804,7 @@
       <c r="A173" s="15"/>
       <c r="B173" s="22"/>
       <c r="C173" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D173" s="18"/>
@@ -15895,7 +15892,7 @@
       <c r="A174" s="15"/>
       <c r="B174" s="22"/>
       <c r="C174" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D174" s="18"/>
@@ -15983,7 +15980,7 @@
       <c r="A175" s="15"/>
       <c r="B175" s="22"/>
       <c r="C175" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D175" s="18"/>
@@ -16071,7 +16068,7 @@
       <c r="A176" s="15"/>
       <c r="B176" s="22"/>
       <c r="C176" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D176" s="18"/>
@@ -16159,7 +16156,7 @@
       <c r="A177" s="15"/>
       <c r="B177" s="22"/>
       <c r="C177" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D177" s="18"/>
@@ -16247,7 +16244,7 @@
       <c r="A178" s="15"/>
       <c r="B178" s="22"/>
       <c r="C178" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D178" s="18"/>
@@ -16335,7 +16332,7 @@
       <c r="A179" s="15"/>
       <c r="B179" s="22"/>
       <c r="C179" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D179" s="18"/>
@@ -16423,7 +16420,7 @@
       <c r="A180" s="15"/>
       <c r="B180" s="22"/>
       <c r="C180" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D180" s="18"/>
@@ -16511,7 +16508,7 @@
       <c r="A181" s="15"/>
       <c r="B181" s="22"/>
       <c r="C181" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D181" s="18"/>
@@ -16599,7 +16596,7 @@
       <c r="A182" s="15"/>
       <c r="B182" s="22"/>
       <c r="C182" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D182" s="18"/>
@@ -16687,7 +16684,7 @@
       <c r="A183" s="15"/>
       <c r="B183" s="22"/>
       <c r="C183" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D183" s="18"/>
@@ -16775,7 +16772,7 @@
       <c r="A184" s="15"/>
       <c r="B184" s="22"/>
       <c r="C184" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D184" s="18"/>
@@ -16863,7 +16860,7 @@
       <c r="A185" s="15"/>
       <c r="B185" s="22"/>
       <c r="C185" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D185" s="18"/>
@@ -16951,7 +16948,7 @@
       <c r="A186" s="15"/>
       <c r="B186" s="22"/>
       <c r="C186" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D186" s="18"/>
@@ -17039,7 +17036,7 @@
       <c r="A187" s="15"/>
       <c r="B187" s="22"/>
       <c r="C187" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D187" s="18"/>
@@ -17127,7 +17124,7 @@
       <c r="A188" s="15"/>
       <c r="B188" s="22"/>
       <c r="C188" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D188" s="18"/>
@@ -17215,7 +17212,7 @@
       <c r="A189" s="15"/>
       <c r="B189" s="22"/>
       <c r="C189" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D189" s="18"/>
@@ -17303,7 +17300,7 @@
       <c r="A190" s="15"/>
       <c r="B190" s="22"/>
       <c r="C190" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D190" s="18"/>
@@ -17391,7 +17388,7 @@
       <c r="A191" s="15"/>
       <c r="B191" s="22"/>
       <c r="C191" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D191" s="18"/>
@@ -17479,7 +17476,7 @@
       <c r="A192" s="15"/>
       <c r="B192" s="22"/>
       <c r="C192" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D192" s="18"/>
@@ -17567,7 +17564,7 @@
       <c r="A193" s="15"/>
       <c r="B193" s="22"/>
       <c r="C193" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D193" s="18"/>
@@ -17655,7 +17652,7 @@
       <c r="A194" s="15"/>
       <c r="B194" s="22"/>
       <c r="C194" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D194" s="18"/>
@@ -17743,7 +17740,7 @@
       <c r="A195" s="15"/>
       <c r="B195" s="22"/>
       <c r="C195" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D195" s="18"/>
@@ -17831,7 +17828,7 @@
       <c r="A196" s="15"/>
       <c r="B196" s="22"/>
       <c r="C196" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D196" s="18"/>
@@ -17919,7 +17916,7 @@
       <c r="A197" s="15"/>
       <c r="B197" s="22"/>
       <c r="C197" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D197" s="18"/>
@@ -18007,7 +18004,7 @@
       <c r="A198" s="15"/>
       <c r="B198" s="22"/>
       <c r="C198" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D198" s="18"/>
@@ -18095,7 +18092,7 @@
       <c r="A199" s="15"/>
       <c r="B199" s="22"/>
       <c r="C199" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D199" s="18"/>
@@ -18183,7 +18180,7 @@
       <c r="A200" s="15"/>
       <c r="B200" s="22"/>
       <c r="C200" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D200" s="18"/>
@@ -18271,7 +18268,7 @@
       <c r="A201" s="15"/>
       <c r="B201" s="22"/>
       <c r="C201" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D201" s="18"/>
@@ -18359,7 +18356,7 @@
       <c r="A202" s="15"/>
       <c r="B202" s="22"/>
       <c r="C202" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D202" s="18"/>
@@ -18447,7 +18444,7 @@
       <c r="A203" s="15"/>
       <c r="B203" s="22"/>
       <c r="C203" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D203" s="18"/>
@@ -18535,7 +18532,7 @@
       <c r="A204" s="15"/>
       <c r="B204" s="22"/>
       <c r="C204" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D204" s="18"/>
@@ -18623,7 +18620,7 @@
       <c r="A205" s="15"/>
       <c r="B205" s="22"/>
       <c r="C205" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D205" s="18"/>
@@ -18711,7 +18708,7 @@
       <c r="A206" s="15"/>
       <c r="B206" s="22"/>
       <c r="C206" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D206" s="18"/>
@@ -18799,7 +18796,7 @@
       <c r="A207" s="15"/>
       <c r="B207" s="22"/>
       <c r="C207" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D207" s="18"/>
@@ -18887,7 +18884,7 @@
       <c r="A208" s="15"/>
       <c r="B208" s="22"/>
       <c r="C208" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D208" s="18"/>
@@ -18975,7 +18972,7 @@
       <c r="A209" s="15"/>
       <c r="B209" s="22"/>
       <c r="C209" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D209" s="18"/>
@@ -19063,7 +19060,7 @@
       <c r="A210" s="15"/>
       <c r="B210" s="22"/>
       <c r="C210" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D210" s="18"/>
@@ -19151,7 +19148,7 @@
       <c r="A211" s="15"/>
       <c r="B211" s="22"/>
       <c r="C211" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D211" s="18"/>
@@ -19239,7 +19236,7 @@
       <c r="A212" s="15"/>
       <c r="B212" s="22"/>
       <c r="C212" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D212" s="18"/>
@@ -19327,7 +19324,7 @@
       <c r="A213" s="15"/>
       <c r="B213" s="22"/>
       <c r="C213" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D213" s="18"/>
@@ -19415,7 +19412,7 @@
       <c r="A214" s="15"/>
       <c r="B214" s="22"/>
       <c r="C214" s="17" t="str">
-        <f aca="true">IF(ISBLANK(INDIRECT("B"&amp;ROW())),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
         <v/>
       </c>
       <c r="D214" s="18"/>
@@ -19499,8 +19496,260 @@
       <c r="CD214" s="20"/>
       <c r="CE214" s="20"/>
     </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C215" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C216" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C217" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C218" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C219" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C220" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C221" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C222" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C223" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C224" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C225" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C226" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C227" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C228" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C229" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C230" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C231" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C232" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C233" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C234" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C235" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C236" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C237" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C238" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C239" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C240" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C241" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C242" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C243" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C244" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C245" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C246" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C247" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C248" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C249" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C250" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C251" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C252" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C253" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C254" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C255" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C256" s="17" t="str">
+        <f aca="true">IF(OR(ISBLANK(INDIRECT("B"&amp;ROW())),INDIRECT("B"&amp;ROW())=0),"",INDIRECT("B"&amp;ROW())-SUM(INDIRECT("E"&amp;ROW()&amp;":YZ"&amp;ROW())))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C3:C214">
+  <conditionalFormatting sqref="C3:C256">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -19518,8 +19767,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/src/fnschool/canteen/data/consuming.xlsx
+++ b/src/fnschool/canteen/data/consuming.xlsx
@@ -19767,8 +19767,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>